--- a/reference/items_recipes_template.xlsx
+++ b/reference/items_recipes_template.xlsx
@@ -4202,9 +4202,13 @@
           <t>中(与液体模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N2" s="5" t="inlineStr"/>
       <c r="O2" s="5" t="inlineStr"/>
     </row>
@@ -4251,10 +4255,18 @@
           <t>中(与基础模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4292,9 +4304,13 @@
       </c>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
     </row>
@@ -4341,9 +4357,13 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
     </row>
@@ -4390,9 +4410,15 @@
           <t>中高(与基础模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
     </row>
@@ -4439,9 +4465,13 @@
           <t>中高(与气体模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
     </row>
@@ -4488,9 +4518,13 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
     </row>
@@ -4537,9 +4571,13 @@
           <t>中高(与液体模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
     </row>
@@ -4586,9 +4624,15 @@
           <t>中高(与基础模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr"/>
     </row>
@@ -4632,10 +4676,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>不需要配方</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4680,9 +4730,13 @@
           <t>中(id字面对不上,按配方内容匹配)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="5" t="inlineStr"/>
     </row>
@@ -4729,9 +4783,13 @@
           <t>中高(与气液模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="5" t="inlineStr"/>
     </row>
@@ -4778,9 +4836,15 @@
           <t>中高(与基础模式是否共享配方待核实)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="5" t="inlineStr"/>
     </row>
@@ -4827,9 +4891,13 @@
           <t>低中(id字面是"工具组装",配方内容更像封装消耗品,存疑)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N15" s="5" t="inlineStr"/>
       <c r="O15" s="5" t="inlineStr"/>
     </row>
@@ -4876,9 +4944,13 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
     </row>
@@ -4927,9 +4999,17 @@
       </c>
       <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
-      <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>反应池共有5个槽位，所有反应池内的原料及产物共享这5个槽位</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4976,9 +5056,17 @@
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>反应池共有8个槽位，所有反应池内的原料及产物共享着8个槽位</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5023,9 +5111,15 @@
           <t>中高</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
     </row>
@@ -5072,10 +5166,16 @@
           <t>中(id字面是"液体"但配方含固体输入,和现有端口对不上"液体"模式,疑似应归到气体模式,需重点核实)</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5118,9 +5218,13 @@
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="O21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5166,10 +5270,16 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5216,9 +5326,13 @@
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5265,9 +5379,13 @@
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5313,10 +5431,14 @@
           <t>中(transmuter_2配方两个方向混在一起,需按输出是气体的方向筛选)</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5363,8 +5485,12 @@
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
     </row>
@@ -5411,7 +5537,11 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>不需要配方</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -5457,9 +5587,13 @@
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O28" s="5" t="inlineStr"/>
     </row>
     <row r="29">

--- a/reference/items_recipes_template.xlsx
+++ b/reference/items_recipes_template.xlsx
@@ -674,7 +674,11 @@
           <t>item_activity_xiranite_bottle</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>实验息壤瓶</t>
+        </is>
+      </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -691,7 +695,11 @@
           <t>item_activity_xiranite_cmpt</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>实验息壤零件</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -708,7 +716,11 @@
           <t>item_activity_xiranite_enr_bottle</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>实验重息壤瓶</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -725,7 +737,11 @@
           <t>item_activity_xiranite_enr_cmpt</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>实验重息壤零件</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -742,7 +758,11 @@
           <t>item_activity_xiranite_enr_hulu</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>息壤玉葫芦</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -759,7 +779,11 @@
           <t>item_activity_xiranite_enr_tool</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>实验玉铜发散器</t>
+        </is>
+      </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -776,7 +800,11 @@
           <t>item_activity_xiranite_hulu</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>息壤葫芦</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -793,7 +821,11 @@
           <t>item_bottled_food_1</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>柑实罐头</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -810,7 +842,11 @@
           <t>item_bottled_food_2</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>优质柑实罐头</t>
+        </is>
+      </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -827,7 +863,11 @@
           <t>item_bottled_food_3</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>精选柑实罐头</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -844,7 +884,11 @@
           <t>item_bottled_food_4</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>锦草软饮</t>
+        </is>
+      </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -861,7 +905,11 @@
           <t>item_bottled_food_5</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>优质锦草软饮</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -878,7 +926,11 @@
           <t>item_bottled_rec_hp_1</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>荞愈胶囊</t>
+        </is>
+      </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -895,7 +947,11 @@
           <t>item_bottled_rec_hp_2</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>优质荞愈胶囊</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -912,7 +968,11 @@
           <t>item_bottled_rec_hp_3</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>精选荞愈胶囊</t>
+        </is>
+      </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -929,7 +989,11 @@
           <t>item_bottled_rec_hp_4</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>芽针针剂</t>
+        </is>
+      </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -946,7 +1010,11 @@
           <t>item_bottled_rec_hp_5</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>优质芽针针剂</t>
+        </is>
+      </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -963,7 +1031,11 @@
           <t>item_carbon_enr</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>稳定碳块</t>
+        </is>
+      </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -980,7 +1052,11 @@
           <t>item_carbon_enr_powder</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>致密碳粉末</t>
+        </is>
+      </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -997,7 +1073,11 @@
           <t>item_carbon_mtl</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>碳块</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1014,7 +1094,11 @@
           <t>item_carbon_powder</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>碳粉末</t>
+        </is>
+      </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1031,7 +1115,11 @@
           <t>item_copper_bottle</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶</t>
+        </is>
+      </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1048,7 +1136,11 @@
           <t>item_copper_cmpt</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>赤铜零件</t>
+        </is>
+      </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1065,7 +1157,11 @@
           <t>item_copper_enr</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>赫铜块</t>
+        </is>
+      </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1082,7 +1178,11 @@
           <t>item_copper_enr2</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>灼铜块</t>
+        </is>
+      </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1099,7 +1199,11 @@
           <t>item_copper_enr2_cmpt</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>灼铜零件</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1116,7 +1220,11 @@
           <t>item_copper_enr_bottle</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶</t>
+        </is>
+      </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1133,7 +1241,11 @@
           <t>item_copper_enr_cmpt</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>赫铜零件</t>
+        </is>
+      </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1150,7 +1262,11 @@
           <t>item_copper_jar</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐</t>
+        </is>
+      </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1167,7 +1283,11 @@
           <t>item_copper_nugget</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>赤铜块</t>
+        </is>
+      </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1184,7 +1304,11 @@
           <t>item_copper_ore</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>赤铜矿</t>
+        </is>
+      </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1201,7 +1325,11 @@
           <t>item_copper_powder</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>赤铜粉末</t>
+        </is>
+      </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1218,7 +1346,11 @@
           <t>item_crystal_enr</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>密制晶体</t>
+        </is>
+      </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1235,7 +1367,11 @@
           <t>item_crystal_enr_powder</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>致密晶体粉末</t>
+        </is>
+      </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1252,7 +1388,11 @@
           <t>item_crystal_powder</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>晶体外壳粉末</t>
+        </is>
+      </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1269,7 +1409,11 @@
           <t>item_crystal_shell</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>晶体外壳</t>
+        </is>
+      </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1286,7 +1430,11 @@
           <t>item_equip_script_1</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>紫晶装备原件</t>
+        </is>
+      </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1303,7 +1451,11 @@
           <t>item_equip_script_2</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁装备原件</t>
+        </is>
+      </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1320,7 +1472,11 @@
           <t>item_equip_script_3</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>高晶装备原件</t>
+        </is>
+      </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1337,7 +1493,11 @@
           <t>item_equip_script_4</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>息壤装备原件</t>
+        </is>
+      </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1354,7 +1514,11 @@
           <t>item_equip_script_4_1</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>赤铜装备原件</t>
+        </is>
+      </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1371,7 +1535,11 @@
           <t>item_equip_script_4_2</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>赫铜装备原件</t>
+        </is>
+      </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1388,7 +1556,11 @@
           <t>item_equip_script_4_3</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>灼铜装备原件</t>
+        </is>
+      </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1405,7 +1577,11 @@
           <t>item_fbottle_copper_acid</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1422,7 +1598,11 @@
           <t>item_fbottle_copper_copper</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1439,7 +1619,11 @@
           <t>item_fbottle_copper_copper_enr</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1456,7 +1640,11 @@
           <t>item_fbottle_copper_grass_1</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1473,7 +1661,11 @@
           <t>item_fbottle_copper_grass_2</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1490,7 +1682,11 @@
           <t>item_fbottle_copper_sewage</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（污水）</t>
+        </is>
+      </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1507,7 +1703,11 @@
           <t>item_fbottle_copper_water</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（清水）</t>
+        </is>
+      </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1524,7 +1724,11 @@
           <t>item_fbottle_copper_xiranite</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1541,7 +1745,11 @@
           <t>item_fbottle_copper_xiranite_enr</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1558,7 +1766,11 @@
           <t>item_fbottle_copper_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1575,7 +1787,11 @@
           <t>item_fbottle_copper_xiranite_poly</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>赤铜瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1592,7 +1808,11 @@
           <t>item_fbottle_copperenr_acid</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1609,7 +1829,11 @@
           <t>item_fbottle_copperenr_copper</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr"/>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1626,7 +1850,11 @@
           <t>item_fbottle_copperenr_copper_enr</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1643,7 +1871,11 @@
           <t>item_fbottle_copperenr_grass_1</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1660,7 +1892,11 @@
           <t>item_fbottle_copperenr_grass_2</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1677,7 +1913,11 @@
           <t>item_fbottle_copperenr_sewage</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr"/>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（污水）</t>
+        </is>
+      </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1694,7 +1934,11 @@
           <t>item_fbottle_copperenr_water</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（清水）</t>
+        </is>
+      </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1711,7 +1955,11 @@
           <t>item_fbottle_copperenr_xiranite</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr"/>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1728,7 +1976,11 @@
           <t>item_fbottle_copperenr_xiranite_enr</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1745,7 +1997,11 @@
           <t>item_fbottle_copperenr_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr"/>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1762,7 +2018,11 @@
           <t>item_fbottle_copperenr_xiranite_poly</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr"/>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>赫铜瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1779,7 +2039,11 @@
           <t>item_fbottle_glass_acid</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr"/>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1796,7 +2060,11 @@
           <t>item_fbottle_glass_copper</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr"/>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1813,7 +2081,11 @@
           <t>item_fbottle_glass_copper_enr</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr"/>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1830,7 +2102,11 @@
           <t>item_fbottle_glass_grass_1</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr"/>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1847,7 +2123,11 @@
           <t>item_fbottle_glass_grass_2</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr"/>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1864,7 +2144,11 @@
           <t>item_fbottle_glass_sewage</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr"/>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（污水）</t>
+        </is>
+      </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1881,7 +2165,11 @@
           <t>item_fbottle_glass_water</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr"/>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（清水）</t>
+        </is>
+      </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1898,7 +2186,11 @@
           <t>item_fbottle_glass_xiranite</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr"/>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1915,7 +2207,11 @@
           <t>item_fbottle_glass_xiranite_enr</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr"/>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1932,7 +2228,11 @@
           <t>item_fbottle_glass_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr"/>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1949,7 +2249,11 @@
           <t>item_fbottle_glass_xiranite_poly</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr"/>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1966,7 +2270,11 @@
           <t>item_fbottle_glassenr_acid</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr"/>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -1983,7 +2291,11 @@
           <t>item_fbottle_glassenr_copper</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr"/>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2000,7 +2312,11 @@
           <t>item_fbottle_glassenr_copper_enr</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr"/>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2017,7 +2333,11 @@
           <t>item_fbottle_glassenr_grass_1</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr"/>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2034,7 +2354,11 @@
           <t>item_fbottle_glassenr_grass_2</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr"/>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2051,7 +2375,11 @@
           <t>item_fbottle_glassenr_sewage</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr"/>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（污水）</t>
+        </is>
+      </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2068,7 +2396,11 @@
           <t>item_fbottle_glassenr_water</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr"/>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（清水）</t>
+        </is>
+      </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2085,7 +2417,11 @@
           <t>item_fbottle_glassenr_xiranite</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr"/>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2102,7 +2438,11 @@
           <t>item_fbottle_glassenr_xiranite_enr</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr"/>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2119,7 +2459,11 @@
           <t>item_fbottle_glassenr_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr"/>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2136,7 +2480,11 @@
           <t>item_fbottle_glassenr_xiranite_poly</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr"/>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2153,7 +2501,11 @@
           <t>item_fbottle_iron_acid</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr"/>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2170,7 +2522,11 @@
           <t>item_fbottle_iron_copper</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr"/>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2187,7 +2543,11 @@
           <t>item_fbottle_iron_copper_enr</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr"/>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2204,7 +2564,11 @@
           <t>item_fbottle_iron_grass_1</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr"/>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2221,7 +2585,11 @@
           <t>item_fbottle_iron_grass_2</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr"/>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2238,7 +2606,11 @@
           <t>item_fbottle_iron_sewage</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr"/>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（污水）</t>
+        </is>
+      </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2255,7 +2627,11 @@
           <t>item_fbottle_iron_water</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr"/>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（清水）</t>
+        </is>
+      </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2272,7 +2648,11 @@
           <t>item_fbottle_iron_xiranite</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr"/>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2289,7 +2669,11 @@
           <t>item_fbottle_iron_xiranite_enr</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr"/>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2306,7 +2690,11 @@
           <t>item_fbottle_iron_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr"/>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2323,7 +2711,11 @@
           <t>item_fbottle_iron_xiranite_poly</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr"/>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2340,7 +2732,11 @@
           <t>item_fbottle_ironenr_acid</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr"/>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（沉积酸）</t>
+        </is>
+      </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2357,7 +2753,11 @@
           <t>item_fbottle_ironenr_copper</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr"/>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（赤铜溶液）</t>
+        </is>
+      </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2374,7 +2774,11 @@
           <t>item_fbottle_ironenr_copper_enr</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr"/>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（赫铜溶液）</t>
+        </is>
+      </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2391,7 +2795,11 @@
           <t>item_fbottle_ironenr_grass_1</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr"/>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（锦草溶液）</t>
+        </is>
+      </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2408,7 +2816,11 @@
           <t>item_fbottle_ironenr_grass_2</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr"/>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2425,7 +2837,11 @@
           <t>item_fbottle_ironenr_sewage</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr"/>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（污水）</t>
+        </is>
+      </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2442,7 +2858,11 @@
           <t>item_fbottle_ironenr_water</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr"/>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（清水）</t>
+        </is>
+      </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2459,7 +2879,11 @@
           <t>item_fbottle_ironenr_xiranite</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr"/>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（液化息壤）</t>
+        </is>
+      </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2476,7 +2900,11 @@
           <t>item_fbottle_ironenr_xiranite_enr</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr"/>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（液化重息壤）</t>
+        </is>
+      </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2493,7 +2921,11 @@
           <t>item_fbottle_ironenr_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr"/>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（壤晶废液）</t>
+        </is>
+      </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2510,7 +2942,11 @@
           <t>item_fbottle_ironenr_xiranite_poly</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr"/>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶（惰性壤晶废液）</t>
+        </is>
+      </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2527,7 +2963,11 @@
           <t>item_fbottle_xiranenr_grass_2</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr"/>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>实验重息壤瓶（芽针溶液）</t>
+        </is>
+      </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2544,7 +2984,11 @@
           <t>item_filter_core</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr"/>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>分离芯</t>
+        </is>
+      </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2561,7 +3005,11 @@
           <t>item_gas_acid</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr"/>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>酸气</t>
+        </is>
+      </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2578,7 +3026,11 @@
           <t>item_gas_copper</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr"/>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>气态赤铜</t>
+        </is>
+      </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2595,7 +3047,11 @@
           <t>item_gas_copper_enr</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr"/>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>气态赫铜</t>
+        </is>
+      </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2612,7 +3068,11 @@
           <t>item_gas_copper_enr2</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr"/>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>气态灼铜</t>
+        </is>
+      </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2629,7 +3089,11 @@
           <t>item_gas_inert</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr"/>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>惰气</t>
+        </is>
+      </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2646,7 +3110,11 @@
           <t>item_gas_water</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr"/>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>水蒸气</t>
+        </is>
+      </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2663,7 +3131,11 @@
           <t>item_gas_xiranite</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr"/>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>息壤气</t>
+        </is>
+      </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2680,7 +3152,11 @@
           <t>item_gas_xiranite_enr</t>
         </is>
       </c>
-      <c r="B120" s="5" t="inlineStr"/>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>重息壤气</t>
+        </is>
+      </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -2697,10 +3173,14 @@
           <t>item_gasjar_copper_gas_acid</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr"/>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（酸气）</t>
+        </is>
+      </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
@@ -2714,10 +3194,14 @@
           <t>item_gasjar_copper_gas_copper</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr"/>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（气态赤铜）</t>
+        </is>
+      </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D122" s="4" t="n">
@@ -2731,10 +3215,14 @@
           <t>item_gasjar_copper_gas_copper_enr</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr"/>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（气态赫铜）</t>
+        </is>
+      </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
@@ -2748,10 +3236,14 @@
           <t>item_gasjar_copper_gas_copper_enr2</t>
         </is>
       </c>
-      <c r="B124" s="5" t="inlineStr"/>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（气态灼铜）</t>
+        </is>
+      </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
@@ -2765,10 +3257,14 @@
           <t>item_gasjar_copper_gas_inert</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr"/>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（惰气）</t>
+        </is>
+      </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
@@ -2782,10 +3278,14 @@
           <t>item_gasjar_copper_gas_water</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr"/>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（水蒸气）</t>
+        </is>
+      </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
@@ -2799,10 +3299,14 @@
           <t>item_gasjar_copper_gas_xiranite</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr"/>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（息壤气）</t>
+        </is>
+      </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
@@ -2816,10 +3320,14 @@
           <t>item_gasjar_copper_gas_xiranite_enr</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr"/>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>赤铜耐压罐（重息壤气）</t>
+        </is>
+      </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="D128" s="4" t="n">
@@ -2833,7 +3341,11 @@
           <t>item_glass_bottle</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr"/>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>紫晶质瓶</t>
+        </is>
+      </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2850,7 +3362,11 @@
           <t>item_glass_cmpt</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr"/>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>紫晶零件</t>
+        </is>
+      </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2867,7 +3383,11 @@
           <t>item_glass_enr_bottle</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr"/>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>高晶质瓶</t>
+        </is>
+      </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2884,7 +3404,11 @@
           <t>item_glass_enr_cmpt</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr"/>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>高晶零件</t>
+        </is>
+      </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2901,7 +3425,11 @@
           <t>item_iron_bottle</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr"/>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁瓶</t>
+        </is>
+      </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2918,7 +3446,11 @@
           <t>item_iron_cmpt</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr"/>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>铁制零件</t>
+        </is>
+      </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2935,7 +3467,11 @@
           <t>item_iron_enr</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr"/>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>钢块</t>
+        </is>
+      </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2952,7 +3488,11 @@
           <t>item_iron_enr_bottle</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr"/>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>钢质瓶</t>
+        </is>
+      </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2969,7 +3509,11 @@
           <t>item_iron_enr_cmpt</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr"/>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>钢制零件</t>
+        </is>
+      </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -2986,7 +3530,11 @@
           <t>item_iron_enr_powder</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr"/>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>致密蓝铁粉末</t>
+        </is>
+      </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3003,7 +3551,11 @@
           <t>item_iron_nugget</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr"/>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁块</t>
+        </is>
+      </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3020,7 +3572,11 @@
           <t>item_iron_ore</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr"/>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁矿</t>
+        </is>
+      </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3037,7 +3593,11 @@
           <t>item_iron_powder</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr"/>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>蓝铁粉末</t>
+        </is>
+      </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3054,7 +3614,11 @@
           <t>item_liquid_acid</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr"/>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>沉积酸</t>
+        </is>
+      </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3071,7 +3635,11 @@
           <t>item_liquid_copper</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr"/>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>赤铜溶液</t>
+        </is>
+      </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3088,7 +3656,11 @@
           <t>item_liquid_copper_enr</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr"/>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>赫铜溶液</t>
+        </is>
+      </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3105,7 +3677,11 @@
           <t>item_liquid_plant_grass_1</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr"/>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>锦草溶液</t>
+        </is>
+      </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3122,7 +3698,11 @@
           <t>item_liquid_plant_grass_2</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr"/>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>芽针溶液</t>
+        </is>
+      </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3139,7 +3719,11 @@
           <t>item_liquid_sewage</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr"/>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>污水</t>
+        </is>
+      </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3156,7 +3740,11 @@
           <t>item_liquid_water</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr"/>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>清水</t>
+        </is>
+      </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3173,7 +3761,11 @@
           <t>item_liquid_xiranite</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr"/>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>液化息壤</t>
+        </is>
+      </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3190,7 +3782,11 @@
           <t>item_liquid_xiranite_enr</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr"/>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>液化重息壤</t>
+        </is>
+      </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3207,7 +3803,11 @@
           <t>item_liquid_xiranite_lowpoly</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr"/>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>惰性壤晶废液</t>
+        </is>
+      </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3224,7 +3824,11 @@
           <t>item_liquid_xiranite_poly</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr"/>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>壤晶废液</t>
+        </is>
+      </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
           <t>fluid</t>
@@ -3241,7 +3845,11 @@
           <t>item_muck_feces_1</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr"/>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>驮兽粪便</t>
+        </is>
+      </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3258,7 +3866,11 @@
           <t>item_muck_xiranite_1</t>
         </is>
       </c>
-      <c r="B154" s="5" t="inlineStr"/>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>膨地啪</t>
+        </is>
+      </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3275,7 +3887,11 @@
           <t>item_originium_enr_powder</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr"/>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>致密源石粉末</t>
+        </is>
+      </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3292,7 +3908,11 @@
           <t>item_originium_ore</t>
         </is>
       </c>
-      <c r="B156" s="5" t="inlineStr"/>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>源矿</t>
+        </is>
+      </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3309,7 +3929,11 @@
           <t>item_originium_powder</t>
         </is>
       </c>
-      <c r="B157" s="5" t="inlineStr"/>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>源石粉末</t>
+        </is>
+      </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3326,7 +3950,11 @@
           <t>item_plant_bbflower_1</t>
         </is>
       </c>
-      <c r="B158" s="5" t="inlineStr"/>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>酮化灌木</t>
+        </is>
+      </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3343,7 +3971,11 @@
           <t>item_plant_bbflower_powder_1</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr"/>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>酮化灌木粉末</t>
+        </is>
+      </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3360,7 +3992,11 @@
           <t>item_plant_bbflower_seed_1</t>
         </is>
       </c>
-      <c r="B160" s="5" t="inlineStr"/>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>酮化树种</t>
+        </is>
+      </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3377,7 +4013,11 @@
           <t>item_plant_grass_1</t>
         </is>
       </c>
-      <c r="B161" s="5" t="inlineStr"/>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>锦草</t>
+        </is>
+      </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3394,7 +4034,11 @@
           <t>item_plant_grass_2</t>
         </is>
       </c>
-      <c r="B162" s="5" t="inlineStr"/>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>芽针</t>
+        </is>
+      </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3411,7 +4055,11 @@
           <t>item_plant_grass_powder_1</t>
         </is>
       </c>
-      <c r="B163" s="5" t="inlineStr"/>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>锦草粉末</t>
+        </is>
+      </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3428,7 +4076,11 @@
           <t>item_plant_grass_powder_2</t>
         </is>
       </c>
-      <c r="B164" s="5" t="inlineStr"/>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>芽针粉末</t>
+        </is>
+      </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3445,7 +4097,11 @@
           <t>item_plant_grass_seed_1</t>
         </is>
       </c>
-      <c r="B165" s="5" t="inlineStr"/>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>锦草种子</t>
+        </is>
+      </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3462,7 +4118,11 @@
           <t>item_plant_grass_seed_2</t>
         </is>
       </c>
-      <c r="B166" s="5" t="inlineStr"/>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>芽针种子</t>
+        </is>
+      </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3479,7 +4139,11 @@
           <t>item_plant_moss_1</t>
         </is>
       </c>
-      <c r="B167" s="5" t="inlineStr"/>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>荞花</t>
+        </is>
+      </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3496,7 +4160,11 @@
           <t>item_plant_moss_2</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr"/>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>柑实</t>
+        </is>
+      </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3513,7 +4181,11 @@
           <t>item_plant_moss_3</t>
         </is>
       </c>
-      <c r="B169" s="5" t="inlineStr"/>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>砂叶</t>
+        </is>
+      </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3530,7 +4202,11 @@
           <t>item_plant_moss_enr_powder_1</t>
         </is>
       </c>
-      <c r="B170" s="5" t="inlineStr"/>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>细磨荞花粉末</t>
+        </is>
+      </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3547,7 +4223,11 @@
           <t>item_plant_moss_enr_powder_2</t>
         </is>
       </c>
-      <c r="B171" s="5" t="inlineStr"/>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>细磨柑实粉末</t>
+        </is>
+      </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3564,7 +4244,11 @@
           <t>item_plant_moss_powder_1</t>
         </is>
       </c>
-      <c r="B172" s="5" t="inlineStr"/>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>荞花粉末</t>
+        </is>
+      </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3581,7 +4265,11 @@
           <t>item_plant_moss_powder_2</t>
         </is>
       </c>
-      <c r="B173" s="5" t="inlineStr"/>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>柑实粉末</t>
+        </is>
+      </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3598,7 +4286,11 @@
           <t>item_plant_moss_powder_3</t>
         </is>
       </c>
-      <c r="B174" s="5" t="inlineStr"/>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>砂叶粉末</t>
+        </is>
+      </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3615,7 +4307,11 @@
           <t>item_plant_moss_seed_1</t>
         </is>
       </c>
-      <c r="B175" s="5" t="inlineStr"/>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>荞花种子</t>
+        </is>
+      </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3632,7 +4328,11 @@
           <t>item_plant_moss_seed_2</t>
         </is>
       </c>
-      <c r="B176" s="5" t="inlineStr"/>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>柑实种子</t>
+        </is>
+      </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3649,7 +4349,11 @@
           <t>item_plant_moss_seed_3</t>
         </is>
       </c>
-      <c r="B177" s="5" t="inlineStr"/>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>砂叶种子</t>
+        </is>
+      </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3666,7 +4370,11 @@
           <t>item_plant_sp_1</t>
         </is>
       </c>
-      <c r="B178" s="5" t="inlineStr"/>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>灰芦麦</t>
+        </is>
+      </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3683,7 +4391,11 @@
           <t>item_plant_sp_2</t>
         </is>
       </c>
-      <c r="B179" s="5" t="inlineStr"/>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>苦叶椒</t>
+        </is>
+      </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3700,7 +4412,11 @@
           <t>item_plant_sp_3</t>
         </is>
       </c>
-      <c r="B180" s="5" t="inlineStr"/>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>琼叶参</t>
+        </is>
+      </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3717,7 +4433,11 @@
           <t>item_plant_sp_4</t>
         </is>
       </c>
-      <c r="B181" s="5" t="inlineStr"/>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>金石稻</t>
+        </is>
+      </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3734,7 +4454,11 @@
           <t>item_plant_sp_seed_1</t>
         </is>
       </c>
-      <c r="B182" s="5" t="inlineStr"/>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>灰芦麦种子</t>
+        </is>
+      </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3751,7 +4475,11 @@
           <t>item_plant_sp_seed_2</t>
         </is>
       </c>
-      <c r="B183" s="5" t="inlineStr"/>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>苦叶椒种子</t>
+        </is>
+      </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3768,7 +4496,11 @@
           <t>item_plant_sp_seed_3</t>
         </is>
       </c>
-      <c r="B184" s="5" t="inlineStr"/>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>琼叶参种子</t>
+        </is>
+      </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3785,7 +4517,11 @@
           <t>item_plant_sp_seed_4</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr"/>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>金石稻种子</t>
+        </is>
+      </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3802,7 +4538,11 @@
           <t>item_plant_tundra_wood</t>
         </is>
       </c>
-      <c r="B186" s="5" t="inlineStr"/>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>原木</t>
+        </is>
+      </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3819,7 +4559,11 @@
           <t>item_proc_battery_1</t>
         </is>
       </c>
-      <c r="B187" s="5" t="inlineStr"/>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>低容谷地电池</t>
+        </is>
+      </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3836,7 +4580,11 @@
           <t>item_proc_battery_2</t>
         </is>
       </c>
-      <c r="B188" s="5" t="inlineStr"/>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>中容谷地电池</t>
+        </is>
+      </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3853,7 +4601,11 @@
           <t>item_proc_battery_3</t>
         </is>
       </c>
-      <c r="B189" s="5" t="inlineStr"/>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>高容谷地电池</t>
+        </is>
+      </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3870,7 +4622,11 @@
           <t>item_proc_battery_4</t>
         </is>
       </c>
-      <c r="B190" s="5" t="inlineStr"/>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>低容武陵电池</t>
+        </is>
+      </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3887,7 +4643,11 @@
           <t>item_proc_battery_5</t>
         </is>
       </c>
-      <c r="B191" s="5" t="inlineStr"/>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>中容武陵电池</t>
+        </is>
+      </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3904,7 +4664,11 @@
           <t>item_proc_bomb_1</t>
         </is>
       </c>
-      <c r="B192" s="5" t="inlineStr"/>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>工业爆炸物</t>
+        </is>
+      </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3921,7 +4685,11 @@
           <t>item_quartz_enr</t>
         </is>
       </c>
-      <c r="B193" s="5" t="inlineStr"/>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>高晶纤维</t>
+        </is>
+      </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3938,7 +4706,11 @@
           <t>item_quartz_enr_powder</t>
         </is>
       </c>
-      <c r="B194" s="5" t="inlineStr"/>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>高晶粉末</t>
+        </is>
+      </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3955,7 +4727,11 @@
           <t>item_quartz_glass</t>
         </is>
       </c>
-      <c r="B195" s="5" t="inlineStr"/>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>紫晶纤维</t>
+        </is>
+      </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3972,7 +4748,11 @@
           <t>item_quartz_powder</t>
         </is>
       </c>
-      <c r="B196" s="5" t="inlineStr"/>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>紫晶粉末</t>
+        </is>
+      </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -3989,7 +4769,11 @@
           <t>item_quartz_sand</t>
         </is>
       </c>
-      <c r="B197" s="5" t="inlineStr"/>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>紫晶矿</t>
+        </is>
+      </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -4006,7 +4790,11 @@
           <t>item_xiranite_enr_powder</t>
         </is>
       </c>
-      <c r="B198" s="5" t="inlineStr"/>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>重息壤</t>
+        </is>
+      </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -4023,7 +4811,11 @@
           <t>item_xiranite_poly</t>
         </is>
       </c>
-      <c r="B199" s="5" t="inlineStr"/>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>壤晶</t>
+        </is>
+      </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
           <t>solid</t>
@@ -4040,7 +4832,11 @@
           <t>item_xiranite_powder</t>
         </is>
       </c>
-      <c r="B200" s="5" t="inlineStr"/>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>息壤</t>
+        </is>
+      </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
           <t>solid</t>

--- a/reference/items_recipes_template.xlsx
+++ b/reference/items_recipes_template.xlsx
@@ -7277,7 +7277,11 @@
       </c>
       <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N2" s="6" t="inlineStr"/>
       <c r="O2" s="5" t="inlineStr"/>
     </row>
@@ -7320,7 +7324,11 @@
       </c>
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N3" s="6" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
     </row>
@@ -7363,7 +7371,11 @@
       </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N4" s="6" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
     </row>
@@ -7406,7 +7418,11 @@
       </c>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N5" s="6" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
     </row>
@@ -7449,7 +7465,11 @@
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N6" s="6" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
     </row>
@@ -7492,7 +7512,11 @@
       </c>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N7" s="6" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
     </row>
@@ -7535,7 +7559,11 @@
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N8" s="6" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
     </row>
@@ -7578,7 +7606,11 @@
       </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N9" s="6" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
     </row>
@@ -7621,7 +7653,11 @@
       </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr"/>
     </row>
@@ -7664,7 +7700,11 @@
       </c>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N11" s="6" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr"/>
     </row>
@@ -7707,7 +7747,11 @@
       </c>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="inlineStr"/>
       <c r="O12" s="5" t="inlineStr"/>
     </row>
@@ -7750,7 +7794,11 @@
       </c>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr"/>
       <c r="O13" s="5" t="inlineStr"/>
     </row>
@@ -7793,7 +7841,11 @@
       </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="inlineStr"/>
       <c r="O14" s="5" t="inlineStr"/>
     </row>
@@ -7836,7 +7888,11 @@
       </c>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="inlineStr"/>
       <c r="O15" s="5" t="inlineStr"/>
     </row>
@@ -7879,7 +7935,11 @@
       </c>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N16" s="6" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
     </row>
@@ -7922,7 +7982,11 @@
       </c>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N17" s="6" t="inlineStr"/>
       <c r="O17" s="5" t="inlineStr"/>
     </row>
@@ -7965,7 +8029,11 @@
       </c>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N18" s="6" t="inlineStr"/>
       <c r="O18" s="5" t="inlineStr"/>
     </row>
@@ -8008,7 +8076,11 @@
       </c>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N19" s="6" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
     </row>
@@ -8063,7 +8135,11 @@
       <c r="L20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_液体</t>
+        </is>
+      </c>
       <c r="N20" s="6" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr"/>
     </row>
@@ -8106,7 +8182,11 @@
       </c>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N21" s="6" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr"/>
     </row>
@@ -8149,7 +8229,11 @@
       </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N22" s="6" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
     </row>
@@ -8192,7 +8276,11 @@
       </c>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N23" s="6" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
     </row>
@@ -8235,7 +8323,11 @@
       </c>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
     </row>
@@ -8278,7 +8370,11 @@
       </c>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N25" s="6" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
     </row>
@@ -8321,7 +8417,11 @@
       </c>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N26" s="6" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
     </row>
@@ -8364,7 +8464,11 @@
       </c>
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>dev_精炼炉_基础</t>
+        </is>
+      </c>
       <c r="N27" s="6" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
     </row>
@@ -8407,7 +8511,11 @@
       </c>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N28" s="6" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr"/>
     </row>
@@ -8450,7 +8558,11 @@
       </c>
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N29" s="6" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
     </row>
@@ -8493,7 +8605,11 @@
       </c>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N30" s="6" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
     </row>
@@ -8536,7 +8652,11 @@
       </c>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N31" s="6" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
     </row>
@@ -8579,7 +8699,11 @@
       </c>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N32" s="6" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
     </row>
@@ -8622,7 +8746,11 @@
       </c>
       <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N33" s="6" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
     </row>
@@ -8665,7 +8793,11 @@
       </c>
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N34" s="6" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
     </row>
@@ -8708,7 +8840,11 @@
       </c>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N35" s="6" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
     </row>
@@ -8751,7 +8887,11 @@
       </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="5" t="inlineStr"/>
     </row>
@@ -8794,7 +8934,11 @@
       </c>
       <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N37" s="6" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
     </row>
@@ -8837,7 +8981,11 @@
       </c>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N38" s="6" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
     </row>
@@ -8880,7 +9028,11 @@
       </c>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>dev_粉碎机</t>
+        </is>
+      </c>
       <c r="N39" s="6" t="inlineStr"/>
       <c r="O39" s="5" t="inlineStr"/>
     </row>
@@ -8923,7 +9075,11 @@
       </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N40" s="6" t="inlineStr"/>
       <c r="O40" s="5" t="inlineStr"/>
     </row>
@@ -8966,7 +9122,11 @@
       </c>
       <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N41" s="6" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
     </row>
@@ -9009,7 +9169,11 @@
       </c>
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N42" s="6" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr"/>
     </row>
@@ -9052,7 +9216,11 @@
       </c>
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N43" s="6" t="inlineStr"/>
       <c r="O43" s="5" t="inlineStr"/>
     </row>
@@ -9095,7 +9263,11 @@
       </c>
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N44" s="6" t="inlineStr"/>
       <c r="O44" s="5" t="inlineStr"/>
     </row>
@@ -9138,7 +9310,11 @@
       </c>
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N45" s="6" t="inlineStr"/>
       <c r="O45" s="5" t="inlineStr"/>
     </row>
@@ -9181,7 +9357,11 @@
       </c>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N46" s="6" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
     </row>
@@ -9224,7 +9404,11 @@
       </c>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N47" s="6" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
     </row>
@@ -9267,7 +9451,11 @@
       </c>
       <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>dev_配件机</t>
+        </is>
+      </c>
       <c r="N48" s="6" t="inlineStr"/>
       <c r="O48" s="5" t="inlineStr"/>
     </row>
@@ -9310,7 +9498,11 @@
       </c>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N49" s="6" t="inlineStr"/>
       <c r="O49" s="5" t="inlineStr"/>
     </row>
@@ -9353,7 +9545,11 @@
       </c>
       <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N50" s="6" t="inlineStr"/>
       <c r="O50" s="5" t="inlineStr"/>
     </row>
@@ -9396,7 +9592,11 @@
       </c>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N51" s="6" t="inlineStr"/>
       <c r="O51" s="5" t="inlineStr"/>
     </row>
@@ -9439,7 +9639,11 @@
       </c>
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N52" s="6" t="inlineStr"/>
       <c r="O52" s="5" t="inlineStr"/>
     </row>
@@ -9482,7 +9686,11 @@
       </c>
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="4" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N53" s="6" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
     </row>
@@ -9531,7 +9739,11 @@
       </c>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_气体</t>
+        </is>
+      </c>
       <c r="N54" s="6" t="inlineStr"/>
       <c r="O54" s="5" t="inlineStr"/>
     </row>
@@ -9574,7 +9786,11 @@
       </c>
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N55" s="6" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
     </row>
@@ -9617,7 +9833,11 @@
       </c>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N56" s="6" t="inlineStr"/>
       <c r="O56" s="5" t="inlineStr"/>
     </row>
@@ -9660,7 +9880,11 @@
       </c>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>dev_塑形机_基础</t>
+        </is>
+      </c>
       <c r="N57" s="6" t="inlineStr"/>
       <c r="O57" s="5" t="inlineStr"/>
     </row>
@@ -9703,7 +9927,11 @@
       </c>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_基础</t>
+        </is>
+      </c>
       <c r="N58" s="6" t="inlineStr"/>
       <c r="O58" s="5" t="inlineStr"/>
     </row>
@@ -9746,7 +9974,11 @@
       </c>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_基础</t>
+        </is>
+      </c>
       <c r="N59" s="6" t="inlineStr"/>
       <c r="O59" s="5" t="inlineStr"/>
     </row>
@@ -9795,7 +10027,11 @@
       </c>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_液体</t>
+        </is>
+      </c>
       <c r="N60" s="6" t="inlineStr"/>
       <c r="O60" s="5" t="inlineStr"/>
     </row>
@@ -9838,7 +10074,11 @@
       </c>
       <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_基础</t>
+        </is>
+      </c>
       <c r="N61" s="6" t="inlineStr"/>
       <c r="O61" s="5" t="inlineStr"/>
     </row>
@@ -9881,7 +10121,11 @@
       </c>
       <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_基础</t>
+        </is>
+      </c>
       <c r="N62" s="6" t="inlineStr"/>
       <c r="O62" s="5" t="inlineStr"/>
     </row>
@@ -9930,7 +10174,11 @@
       </c>
       <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>dev_种植机_液体</t>
+        </is>
+      </c>
       <c r="N63" s="6" t="inlineStr"/>
       <c r="O63" s="5" t="inlineStr"/>
     </row>
@@ -9973,7 +10221,11 @@
       </c>
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N64" s="6" t="inlineStr"/>
       <c r="O64" s="5" t="inlineStr"/>
     </row>
@@ -10016,7 +10268,11 @@
       </c>
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N65" s="6" t="inlineStr"/>
       <c r="O65" s="5" t="inlineStr"/>
     </row>
@@ -10059,7 +10315,11 @@
       </c>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N66" s="6" t="inlineStr"/>
       <c r="O66" s="5" t="inlineStr"/>
     </row>
@@ -10102,7 +10362,11 @@
       </c>
       <c r="K67" s="4" t="inlineStr"/>
       <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N67" s="6" t="inlineStr"/>
       <c r="O67" s="5" t="inlineStr"/>
     </row>
@@ -10145,7 +10409,11 @@
       </c>
       <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N68" s="6" t="inlineStr"/>
       <c r="O68" s="5" t="inlineStr"/>
     </row>
@@ -10188,7 +10456,11 @@
       </c>
       <c r="K69" s="4" t="inlineStr"/>
       <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N69" s="6" t="inlineStr"/>
       <c r="O69" s="5" t="inlineStr"/>
     </row>
@@ -10231,7 +10503,11 @@
       </c>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N70" s="6" t="inlineStr"/>
       <c r="O70" s="5" t="inlineStr"/>
     </row>
@@ -10274,7 +10550,11 @@
       </c>
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="5" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N71" s="6" t="inlineStr"/>
       <c r="O71" s="5" t="inlineStr"/>
     </row>
@@ -10317,7 +10597,11 @@
       </c>
       <c r="K72" s="4" t="inlineStr"/>
       <c r="L72" s="4" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N72" s="6" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
     </row>
@@ -10360,7 +10644,11 @@
       </c>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="5" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>dev_采种机</t>
+        </is>
+      </c>
       <c r="N73" s="6" t="inlineStr"/>
       <c r="O73" s="5" t="inlineStr"/>
     </row>
@@ -10409,7 +10697,11 @@
       </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N74" s="6" t="inlineStr"/>
       <c r="O74" s="5" t="inlineStr"/>
     </row>
@@ -10458,7 +10750,11 @@
       </c>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N75" s="6" t="inlineStr"/>
       <c r="O75" s="5" t="inlineStr"/>
     </row>
@@ -10507,7 +10803,11 @@
       </c>
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="5" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N76" s="6" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr"/>
     </row>
@@ -10556,7 +10856,11 @@
       </c>
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N77" s="6" t="inlineStr"/>
       <c r="O77" s="5" t="inlineStr"/>
     </row>
@@ -10605,7 +10909,11 @@
       </c>
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N78" s="6" t="inlineStr"/>
       <c r="O78" s="5" t="inlineStr"/>
     </row>
@@ -10654,7 +10962,11 @@
       </c>
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="5" t="inlineStr"/>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N79" s="6" t="inlineStr"/>
       <c r="O79" s="5" t="inlineStr"/>
     </row>
@@ -10703,7 +11015,11 @@
       </c>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>dev_装备原件机</t>
+        </is>
+      </c>
       <c r="N80" s="6" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
     </row>
@@ -10752,7 +11068,11 @@
       </c>
       <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="4" t="inlineStr"/>
-      <c r="M81" s="5" t="inlineStr"/>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N81" s="6" t="inlineStr"/>
       <c r="O81" s="5" t="inlineStr"/>
     </row>
@@ -10801,7 +11121,11 @@
       </c>
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N82" s="6" t="inlineStr"/>
       <c r="O82" s="5" t="inlineStr"/>
     </row>
@@ -10850,7 +11174,11 @@
       </c>
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N83" s="6" t="inlineStr"/>
       <c r="O83" s="5" t="inlineStr"/>
     </row>
@@ -10899,7 +11227,11 @@
       </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N84" s="6" t="inlineStr"/>
       <c r="O84" s="5" t="inlineStr"/>
     </row>
@@ -10948,7 +11280,11 @@
       </c>
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="5" t="inlineStr"/>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N85" s="6" t="inlineStr"/>
       <c r="O85" s="5" t="inlineStr"/>
     </row>
@@ -10997,7 +11333,11 @@
       </c>
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="5" t="inlineStr"/>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N86" s="6" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
     </row>
@@ -11046,7 +11386,11 @@
       </c>
       <c r="K87" s="4" t="inlineStr"/>
       <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="5" t="inlineStr"/>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N87" s="6" t="inlineStr"/>
       <c r="O87" s="5" t="inlineStr"/>
     </row>
@@ -11095,7 +11439,11 @@
       </c>
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="5" t="inlineStr"/>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N88" s="6" t="inlineStr"/>
       <c r="O88" s="5" t="inlineStr"/>
     </row>
@@ -11144,7 +11492,11 @@
       </c>
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="5" t="inlineStr"/>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N89" s="6" t="inlineStr"/>
       <c r="O89" s="5" t="inlineStr"/>
     </row>
@@ -11193,7 +11545,11 @@
       </c>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="5" t="inlineStr"/>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N90" s="6" t="inlineStr"/>
       <c r="O90" s="5" t="inlineStr"/>
     </row>
@@ -11242,7 +11598,11 @@
       </c>
       <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="5" t="inlineStr"/>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N91" s="6" t="inlineStr"/>
       <c r="O91" s="5" t="inlineStr"/>
     </row>
@@ -11291,7 +11651,11 @@
       </c>
       <c r="K92" s="4" t="inlineStr"/>
       <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N92" s="6" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
     </row>
@@ -11340,7 +11704,11 @@
       </c>
       <c r="K93" s="4" t="inlineStr"/>
       <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="5" t="inlineStr"/>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N93" s="6" t="inlineStr"/>
       <c r="O93" s="5" t="inlineStr"/>
     </row>
@@ -11389,7 +11757,11 @@
       </c>
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N94" s="6" t="inlineStr"/>
       <c r="O94" s="5" t="inlineStr"/>
     </row>
@@ -11438,7 +11810,11 @@
       </c>
       <c r="K95" s="4" t="inlineStr"/>
       <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="5" t="inlineStr"/>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N95" s="6" t="inlineStr"/>
       <c r="O95" s="5" t="inlineStr"/>
     </row>
@@ -11487,7 +11863,11 @@
       </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="4" t="inlineStr"/>
-      <c r="M96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N96" s="6" t="inlineStr"/>
       <c r="O96" s="5" t="inlineStr"/>
     </row>
@@ -11536,7 +11916,11 @@
       </c>
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="4" t="inlineStr"/>
-      <c r="M97" s="5" t="inlineStr"/>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N97" s="6" t="inlineStr"/>
       <c r="O97" s="5" t="inlineStr"/>
     </row>
@@ -11585,7 +11969,11 @@
       </c>
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="5" t="inlineStr"/>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N98" s="6" t="inlineStr"/>
       <c r="O98" s="5" t="inlineStr"/>
     </row>
@@ -11634,7 +12022,11 @@
       </c>
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr"/>
-      <c r="M99" s="5" t="inlineStr"/>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N99" s="6" t="inlineStr"/>
       <c r="O99" s="5" t="inlineStr"/>
     </row>
@@ -11683,7 +12075,11 @@
       </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="5" t="inlineStr"/>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N100" s="6" t="inlineStr"/>
       <c r="O100" s="5" t="inlineStr"/>
     </row>
@@ -11732,7 +12128,11 @@
       </c>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="5" t="inlineStr"/>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N101" s="6" t="inlineStr"/>
       <c r="O101" s="5" t="inlineStr"/>
     </row>
@@ -11781,7 +12181,11 @@
       </c>
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr"/>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N102" s="6" t="inlineStr"/>
       <c r="O102" s="5" t="inlineStr"/>
     </row>
@@ -11830,7 +12234,11 @@
       </c>
       <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="4" t="inlineStr"/>
-      <c r="M103" s="5" t="inlineStr"/>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N103" s="6" t="inlineStr"/>
       <c r="O103" s="5" t="inlineStr"/>
     </row>
@@ -11879,7 +12287,11 @@
       </c>
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="5" t="inlineStr"/>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N104" s="6" t="inlineStr"/>
       <c r="O104" s="5" t="inlineStr"/>
     </row>
@@ -11928,7 +12340,11 @@
       </c>
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="4" t="inlineStr"/>
-      <c r="M105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N105" s="6" t="inlineStr"/>
       <c r="O105" s="5" t="inlineStr"/>
     </row>
@@ -11977,7 +12393,11 @@
       </c>
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N106" s="6" t="inlineStr"/>
       <c r="O106" s="5" t="inlineStr"/>
     </row>
@@ -12026,7 +12446,11 @@
       </c>
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="4" t="inlineStr"/>
-      <c r="M107" s="5" t="inlineStr"/>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N107" s="6" t="inlineStr"/>
       <c r="O107" s="5" t="inlineStr"/>
     </row>
@@ -12075,7 +12499,11 @@
       </c>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="5" t="inlineStr"/>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N108" s="6" t="inlineStr"/>
       <c r="O108" s="5" t="inlineStr"/>
     </row>
@@ -12124,7 +12552,11 @@
       </c>
       <c r="K109" s="4" t="inlineStr"/>
       <c r="L109" s="4" t="inlineStr"/>
-      <c r="M109" s="5" t="inlineStr"/>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N109" s="6" t="inlineStr"/>
       <c r="O109" s="5" t="inlineStr"/>
     </row>
@@ -12173,7 +12605,11 @@
       </c>
       <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N110" s="6" t="inlineStr"/>
       <c r="O110" s="5" t="inlineStr"/>
     </row>
@@ -12222,7 +12658,11 @@
       </c>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="5" t="inlineStr"/>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N111" s="6" t="inlineStr"/>
       <c r="O111" s="5" t="inlineStr"/>
     </row>
@@ -12271,7 +12711,11 @@
       </c>
       <c r="K112" s="4" t="inlineStr"/>
       <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="5" t="inlineStr"/>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N112" s="6" t="inlineStr"/>
       <c r="O112" s="5" t="inlineStr"/>
     </row>
@@ -12320,7 +12764,11 @@
       </c>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="4" t="inlineStr"/>
-      <c r="M113" s="5" t="inlineStr"/>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N113" s="6" t="inlineStr"/>
       <c r="O113" s="5" t="inlineStr"/>
     </row>
@@ -12369,7 +12817,11 @@
       </c>
       <c r="K114" s="4" t="inlineStr"/>
       <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="5" t="inlineStr"/>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N114" s="6" t="inlineStr"/>
       <c r="O114" s="5" t="inlineStr"/>
     </row>
@@ -12418,7 +12870,11 @@
       </c>
       <c r="K115" s="4" t="inlineStr"/>
       <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="5" t="inlineStr"/>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N115" s="6" t="inlineStr"/>
       <c r="O115" s="5" t="inlineStr"/>
     </row>
@@ -12467,7 +12923,11 @@
       </c>
       <c r="K116" s="4" t="inlineStr"/>
       <c r="L116" s="4" t="inlineStr"/>
-      <c r="M116" s="5" t="inlineStr"/>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N116" s="6" t="inlineStr"/>
       <c r="O116" s="5" t="inlineStr"/>
     </row>
@@ -12516,7 +12976,11 @@
       </c>
       <c r="K117" s="4" t="inlineStr"/>
       <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="5" t="inlineStr"/>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N117" s="6" t="inlineStr"/>
       <c r="O117" s="5" t="inlineStr"/>
     </row>
@@ -12565,7 +13029,11 @@
       </c>
       <c r="K118" s="4" t="inlineStr"/>
       <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N118" s="6" t="inlineStr"/>
       <c r="O118" s="5" t="inlineStr"/>
     </row>
@@ -12614,7 +13082,11 @@
       </c>
       <c r="K119" s="4" t="inlineStr"/>
       <c r="L119" s="4" t="inlineStr"/>
-      <c r="M119" s="5" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N119" s="6" t="inlineStr"/>
       <c r="O119" s="5" t="inlineStr"/>
     </row>
@@ -12663,7 +13135,11 @@
       </c>
       <c r="K120" s="4" t="inlineStr"/>
       <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="5" t="inlineStr"/>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N120" s="6" t="inlineStr"/>
       <c r="O120" s="5" t="inlineStr"/>
     </row>
@@ -12712,7 +13188,11 @@
       </c>
       <c r="K121" s="4" t="inlineStr"/>
       <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N121" s="6" t="inlineStr"/>
       <c r="O121" s="5" t="inlineStr"/>
     </row>
@@ -12761,7 +13241,11 @@
       </c>
       <c r="K122" s="4" t="inlineStr"/>
       <c r="L122" s="4" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N122" s="6" t="inlineStr"/>
       <c r="O122" s="5" t="inlineStr"/>
     </row>
@@ -12810,7 +13294,11 @@
       </c>
       <c r="K123" s="4" t="inlineStr"/>
       <c r="L123" s="4" t="inlineStr"/>
-      <c r="M123" s="5" t="inlineStr"/>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N123" s="6" t="inlineStr"/>
       <c r="O123" s="5" t="inlineStr"/>
     </row>
@@ -12859,7 +13347,11 @@
       </c>
       <c r="K124" s="4" t="inlineStr"/>
       <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="5" t="inlineStr"/>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N124" s="6" t="inlineStr"/>
       <c r="O124" s="5" t="inlineStr"/>
     </row>
@@ -12908,7 +13400,11 @@
       </c>
       <c r="K125" s="4" t="inlineStr"/>
       <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N125" s="6" t="inlineStr"/>
       <c r="O125" s="5" t="inlineStr"/>
     </row>
@@ -12957,7 +13453,11 @@
       </c>
       <c r="K126" s="4" t="inlineStr"/>
       <c r="L126" s="4" t="inlineStr"/>
-      <c r="M126" s="5" t="inlineStr"/>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N126" s="6" t="inlineStr"/>
       <c r="O126" s="5" t="inlineStr"/>
     </row>
@@ -13006,7 +13506,11 @@
       </c>
       <c r="K127" s="4" t="inlineStr"/>
       <c r="L127" s="4" t="inlineStr"/>
-      <c r="M127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N127" s="6" t="inlineStr"/>
       <c r="O127" s="5" t="inlineStr"/>
     </row>
@@ -13055,7 +13559,11 @@
       </c>
       <c r="K128" s="4" t="inlineStr"/>
       <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="5" t="inlineStr"/>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N128" s="6" t="inlineStr"/>
       <c r="O128" s="5" t="inlineStr"/>
     </row>
@@ -13104,7 +13612,11 @@
       </c>
       <c r="K129" s="4" t="inlineStr"/>
       <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="5" t="inlineStr"/>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N129" s="6" t="inlineStr"/>
       <c r="O129" s="5" t="inlineStr"/>
     </row>
@@ -13153,7 +13665,11 @@
       </c>
       <c r="K130" s="4" t="inlineStr"/>
       <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="5" t="inlineStr"/>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N130" s="6" t="inlineStr"/>
       <c r="O130" s="5" t="inlineStr"/>
     </row>
@@ -13202,7 +13718,11 @@
       </c>
       <c r="K131" s="4" t="inlineStr"/>
       <c r="L131" s="4" t="inlineStr"/>
-      <c r="M131" s="5" t="inlineStr"/>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N131" s="6" t="inlineStr"/>
       <c r="O131" s="5" t="inlineStr"/>
     </row>
@@ -13251,7 +13771,11 @@
       </c>
       <c r="K132" s="4" t="inlineStr"/>
       <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="5" t="inlineStr"/>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N132" s="6" t="inlineStr"/>
       <c r="O132" s="5" t="inlineStr"/>
     </row>
@@ -13300,7 +13824,11 @@
       </c>
       <c r="K133" s="4" t="inlineStr"/>
       <c r="L133" s="4" t="inlineStr"/>
-      <c r="M133" s="5" t="inlineStr"/>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N133" s="6" t="inlineStr"/>
       <c r="O133" s="5" t="inlineStr"/>
     </row>
@@ -13349,7 +13877,11 @@
       </c>
       <c r="K134" s="4" t="inlineStr"/>
       <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="5" t="inlineStr"/>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N134" s="6" t="inlineStr"/>
       <c r="O134" s="5" t="inlineStr"/>
     </row>
@@ -13398,7 +13930,11 @@
       </c>
       <c r="K135" s="4" t="inlineStr"/>
       <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="5" t="inlineStr"/>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N135" s="6" t="inlineStr"/>
       <c r="O135" s="5" t="inlineStr"/>
     </row>
@@ -13447,7 +13983,11 @@
       </c>
       <c r="K136" s="4" t="inlineStr"/>
       <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr"/>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N136" s="6" t="inlineStr"/>
       <c r="O136" s="5" t="inlineStr"/>
     </row>
@@ -13496,7 +14036,11 @@
       </c>
       <c r="K137" s="4" t="inlineStr"/>
       <c r="L137" s="4" t="inlineStr"/>
-      <c r="M137" s="5" t="inlineStr"/>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N137" s="6" t="inlineStr"/>
       <c r="O137" s="5" t="inlineStr"/>
     </row>
@@ -13545,7 +14089,11 @@
       </c>
       <c r="K138" s="4" t="inlineStr"/>
       <c r="L138" s="4" t="inlineStr"/>
-      <c r="M138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N138" s="6" t="inlineStr"/>
       <c r="O138" s="5" t="inlineStr"/>
     </row>
@@ -13594,7 +14142,11 @@
       </c>
       <c r="K139" s="4" t="inlineStr"/>
       <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="5" t="inlineStr"/>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N139" s="6" t="inlineStr"/>
       <c r="O139" s="5" t="inlineStr"/>
     </row>
@@ -13643,7 +14195,11 @@
       </c>
       <c r="K140" s="4" t="inlineStr"/>
       <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="5" t="inlineStr"/>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N140" s="6" t="inlineStr"/>
       <c r="O140" s="5" t="inlineStr"/>
     </row>
@@ -13692,7 +14248,11 @@
       </c>
       <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="5" t="inlineStr"/>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N141" s="6" t="inlineStr"/>
       <c r="O141" s="5" t="inlineStr"/>
     </row>
@@ -13741,7 +14301,11 @@
       </c>
       <c r="K142" s="4" t="inlineStr"/>
       <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="5" t="inlineStr"/>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N142" s="6" t="inlineStr"/>
       <c r="O142" s="5" t="inlineStr"/>
     </row>
@@ -13790,7 +14354,11 @@
       </c>
       <c r="K143" s="4" t="inlineStr"/>
       <c r="L143" s="4" t="inlineStr"/>
-      <c r="M143" s="5" t="inlineStr"/>
+      <c r="M143" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N143" s="6" t="inlineStr"/>
       <c r="O143" s="5" t="inlineStr"/>
     </row>
@@ -13839,7 +14407,11 @@
       </c>
       <c r="K144" s="4" t="inlineStr"/>
       <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="5" t="inlineStr"/>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N144" s="6" t="inlineStr"/>
       <c r="O144" s="5" t="inlineStr"/>
     </row>
@@ -13888,7 +14460,11 @@
       </c>
       <c r="K145" s="4" t="inlineStr"/>
       <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="5" t="inlineStr"/>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N145" s="6" t="inlineStr"/>
       <c r="O145" s="5" t="inlineStr"/>
     </row>
@@ -13937,7 +14513,11 @@
       </c>
       <c r="K146" s="4" t="inlineStr"/>
       <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="5" t="inlineStr"/>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N146" s="6" t="inlineStr"/>
       <c r="O146" s="5" t="inlineStr"/>
     </row>
@@ -13986,7 +14566,11 @@
       </c>
       <c r="K147" s="4" t="inlineStr"/>
       <c r="L147" s="4" t="inlineStr"/>
-      <c r="M147" s="5" t="inlineStr"/>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N147" s="6" t="inlineStr"/>
       <c r="O147" s="5" t="inlineStr"/>
     </row>
@@ -14035,7 +14619,11 @@
       </c>
       <c r="K148" s="4" t="inlineStr"/>
       <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="5" t="inlineStr"/>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N148" s="6" t="inlineStr"/>
       <c r="O148" s="5" t="inlineStr"/>
     </row>
@@ -14084,7 +14672,11 @@
       </c>
       <c r="K149" s="4" t="inlineStr"/>
       <c r="L149" s="4" t="inlineStr"/>
-      <c r="M149" s="5" t="inlineStr"/>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N149" s="6" t="inlineStr"/>
       <c r="O149" s="5" t="inlineStr"/>
     </row>
@@ -14133,7 +14725,11 @@
       </c>
       <c r="K150" s="4" t="inlineStr"/>
       <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="5" t="inlineStr"/>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N150" s="6" t="inlineStr"/>
       <c r="O150" s="5" t="inlineStr"/>
     </row>
@@ -14182,7 +14778,11 @@
       </c>
       <c r="K151" s="4" t="inlineStr"/>
       <c r="L151" s="4" t="inlineStr"/>
-      <c r="M151" s="5" t="inlineStr"/>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N151" s="6" t="inlineStr"/>
       <c r="O151" s="5" t="inlineStr"/>
     </row>
@@ -14231,7 +14831,11 @@
       </c>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr"/>
-      <c r="M152" s="5" t="inlineStr"/>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N152" s="6" t="inlineStr"/>
       <c r="O152" s="5" t="inlineStr"/>
     </row>
@@ -14280,7 +14884,11 @@
       </c>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="4" t="inlineStr"/>
-      <c r="M153" s="5" t="inlineStr"/>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N153" s="6" t="inlineStr"/>
       <c r="O153" s="5" t="inlineStr"/>
     </row>
@@ -14329,7 +14937,11 @@
       </c>
       <c r="K154" s="4" t="inlineStr"/>
       <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="5" t="inlineStr"/>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N154" s="6" t="inlineStr"/>
       <c r="O154" s="5" t="inlineStr"/>
     </row>
@@ -14378,7 +14990,11 @@
       </c>
       <c r="K155" s="4" t="inlineStr"/>
       <c r="L155" s="4" t="inlineStr"/>
-      <c r="M155" s="5" t="inlineStr"/>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N155" s="6" t="inlineStr"/>
       <c r="O155" s="5" t="inlineStr"/>
     </row>
@@ -14427,7 +15043,11 @@
       </c>
       <c r="K156" s="4" t="inlineStr"/>
       <c r="L156" s="4" t="inlineStr"/>
-      <c r="M156" s="5" t="inlineStr"/>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_基础</t>
+        </is>
+      </c>
       <c r="N156" s="6" t="inlineStr"/>
       <c r="O156" s="5" t="inlineStr"/>
     </row>
@@ -14476,7 +15096,11 @@
       </c>
       <c r="K157" s="4" t="inlineStr"/>
       <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="5" t="inlineStr"/>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N157" s="6" t="inlineStr"/>
       <c r="O157" s="5" t="inlineStr"/>
     </row>
@@ -14525,7 +15149,11 @@
       </c>
       <c r="K158" s="4" t="inlineStr"/>
       <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="5" t="inlineStr"/>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N158" s="6" t="inlineStr"/>
       <c r="O158" s="5" t="inlineStr"/>
     </row>
@@ -14574,7 +15202,11 @@
       </c>
       <c r="K159" s="4" t="inlineStr"/>
       <c r="L159" s="4" t="inlineStr"/>
-      <c r="M159" s="5" t="inlineStr"/>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N159" s="6" t="inlineStr"/>
       <c r="O159" s="5" t="inlineStr"/>
     </row>
@@ -14623,7 +15255,11 @@
       </c>
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="4" t="inlineStr"/>
-      <c r="M160" s="5" t="inlineStr"/>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N160" s="6" t="inlineStr"/>
       <c r="O160" s="5" t="inlineStr"/>
     </row>
@@ -14672,7 +15308,11 @@
       </c>
       <c r="K161" s="4" t="inlineStr"/>
       <c r="L161" s="4" t="inlineStr"/>
-      <c r="M161" s="5" t="inlineStr"/>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>dev_灌装机_气液</t>
+        </is>
+      </c>
       <c r="N161" s="6" t="inlineStr"/>
       <c r="O161" s="5" t="inlineStr"/>
     </row>
@@ -14721,7 +15361,11 @@
       </c>
       <c r="K162" s="4" t="inlineStr"/>
       <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="5" t="inlineStr"/>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N162" s="6" t="inlineStr"/>
       <c r="O162" s="5" t="inlineStr"/>
     </row>
@@ -14770,7 +15414,11 @@
       </c>
       <c r="K163" s="4" t="inlineStr"/>
       <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="5" t="inlineStr"/>
+      <c r="M163" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N163" s="6" t="inlineStr"/>
       <c r="O163" s="5" t="inlineStr"/>
     </row>
@@ -14819,7 +15467,11 @@
       </c>
       <c r="K164" s="4" t="inlineStr"/>
       <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="5" t="inlineStr"/>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N164" s="6" t="inlineStr"/>
       <c r="O164" s="5" t="inlineStr"/>
     </row>
@@ -14868,7 +15520,11 @@
       </c>
       <c r="K165" s="4" t="inlineStr"/>
       <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="5" t="inlineStr"/>
+      <c r="M165" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N165" s="6" t="inlineStr"/>
       <c r="O165" s="5" t="inlineStr"/>
     </row>
@@ -14917,7 +15573,11 @@
       </c>
       <c r="K166" s="4" t="inlineStr"/>
       <c r="L166" s="4" t="inlineStr"/>
-      <c r="M166" s="5" t="inlineStr"/>
+      <c r="M166" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N166" s="6" t="inlineStr"/>
       <c r="O166" s="5" t="inlineStr"/>
     </row>
@@ -14966,7 +15626,11 @@
       </c>
       <c r="K167" s="4" t="inlineStr"/>
       <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="5" t="inlineStr"/>
+      <c r="M167" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N167" s="6" t="inlineStr"/>
       <c r="O167" s="5" t="inlineStr"/>
     </row>
@@ -15015,7 +15679,11 @@
       </c>
       <c r="K168" s="4" t="inlineStr"/>
       <c r="L168" s="4" t="inlineStr"/>
-      <c r="M168" s="5" t="inlineStr"/>
+      <c r="M168" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N168" s="6" t="inlineStr"/>
       <c r="O168" s="5" t="inlineStr"/>
     </row>
@@ -15064,7 +15732,11 @@
       </c>
       <c r="K169" s="4" t="inlineStr"/>
       <c r="L169" s="4" t="inlineStr"/>
-      <c r="M169" s="5" t="inlineStr"/>
+      <c r="M169" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N169" s="6" t="inlineStr"/>
       <c r="O169" s="5" t="inlineStr"/>
     </row>
@@ -15113,7 +15785,11 @@
       </c>
       <c r="K170" s="4" t="inlineStr"/>
       <c r="L170" s="4" t="inlineStr"/>
-      <c r="M170" s="5" t="inlineStr"/>
+      <c r="M170" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N170" s="6" t="inlineStr"/>
       <c r="O170" s="5" t="inlineStr"/>
     </row>
@@ -15162,7 +15838,11 @@
       </c>
       <c r="K171" s="4" t="inlineStr"/>
       <c r="L171" s="4" t="inlineStr"/>
-      <c r="M171" s="5" t="inlineStr"/>
+      <c r="M171" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N171" s="6" t="inlineStr"/>
       <c r="O171" s="5" t="inlineStr"/>
     </row>
@@ -15211,7 +15891,11 @@
       </c>
       <c r="K172" s="4" t="inlineStr"/>
       <c r="L172" s="4" t="inlineStr"/>
-      <c r="M172" s="5" t="inlineStr"/>
+      <c r="M172" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N172" s="6" t="inlineStr"/>
       <c r="O172" s="5" t="inlineStr"/>
     </row>
@@ -15260,7 +15944,11 @@
       </c>
       <c r="K173" s="4" t="inlineStr"/>
       <c r="L173" s="4" t="inlineStr"/>
-      <c r="M173" s="5" t="inlineStr"/>
+      <c r="M173" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N173" s="6" t="inlineStr"/>
       <c r="O173" s="5" t="inlineStr"/>
     </row>
@@ -15309,7 +15997,11 @@
       </c>
       <c r="K174" s="4" t="inlineStr"/>
       <c r="L174" s="4" t="inlineStr"/>
-      <c r="M174" s="5" t="inlineStr"/>
+      <c r="M174" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N174" s="6" t="inlineStr"/>
       <c r="O174" s="5" t="inlineStr"/>
     </row>
@@ -15358,7 +16050,11 @@
       </c>
       <c r="K175" s="4" t="inlineStr"/>
       <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="5" t="inlineStr"/>
+      <c r="M175" s="5" t="inlineStr">
+        <is>
+          <t>dev_封装机</t>
+        </is>
+      </c>
       <c r="N175" s="6" t="inlineStr"/>
       <c r="O175" s="5" t="inlineStr"/>
     </row>
@@ -15407,7 +16103,11 @@
       </c>
       <c r="K176" s="4" t="inlineStr"/>
       <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="5" t="inlineStr"/>
+      <c r="M176" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N176" s="6" t="inlineStr"/>
       <c r="O176" s="5" t="inlineStr"/>
     </row>
@@ -15456,7 +16156,11 @@
       </c>
       <c r="K177" s="4" t="inlineStr"/>
       <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="5" t="inlineStr"/>
+      <c r="M177" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N177" s="6" t="inlineStr"/>
       <c r="O177" s="5" t="inlineStr"/>
     </row>
@@ -15505,7 +16209,11 @@
       </c>
       <c r="K178" s="4" t="inlineStr"/>
       <c r="L178" s="4" t="inlineStr"/>
-      <c r="M178" s="5" t="inlineStr"/>
+      <c r="M178" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N178" s="6" t="inlineStr"/>
       <c r="O178" s="5" t="inlineStr"/>
     </row>
@@ -15554,7 +16262,11 @@
       </c>
       <c r="K179" s="4" t="inlineStr"/>
       <c r="L179" s="4" t="inlineStr"/>
-      <c r="M179" s="5" t="inlineStr"/>
+      <c r="M179" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N179" s="6" t="inlineStr"/>
       <c r="O179" s="5" t="inlineStr"/>
     </row>
@@ -15603,7 +16315,11 @@
       </c>
       <c r="K180" s="4" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr"/>
-      <c r="M180" s="5" t="inlineStr"/>
+      <c r="M180" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N180" s="6" t="inlineStr"/>
       <c r="O180" s="5" t="inlineStr"/>
     </row>
@@ -15652,7 +16368,11 @@
       </c>
       <c r="K181" s="4" t="inlineStr"/>
       <c r="L181" s="4" t="inlineStr"/>
-      <c r="M181" s="5" t="inlineStr"/>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N181" s="6" t="inlineStr"/>
       <c r="O181" s="5" t="inlineStr"/>
     </row>
@@ -15701,7 +16421,11 @@
       </c>
       <c r="K182" s="4" t="inlineStr"/>
       <c r="L182" s="4" t="inlineStr"/>
-      <c r="M182" s="5" t="inlineStr"/>
+      <c r="M182" s="5" t="inlineStr">
+        <is>
+          <t>dev_研磨机</t>
+        </is>
+      </c>
       <c r="N182" s="6" t="inlineStr"/>
       <c r="O182" s="5" t="inlineStr"/>
     </row>
@@ -15750,7 +16474,11 @@
       </c>
       <c r="K183" s="4" t="inlineStr"/>
       <c r="L183" s="4" t="inlineStr"/>
-      <c r="M183" s="5" t="inlineStr"/>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N183" s="6" t="inlineStr"/>
       <c r="O183" s="5" t="inlineStr"/>
     </row>
@@ -15805,7 +16533,11 @@
       <c r="L184" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M184" s="5" t="inlineStr"/>
+      <c r="M184" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N184" s="6" t="inlineStr"/>
       <c r="O184" s="5" t="inlineStr"/>
     </row>
@@ -15854,7 +16586,11 @@
       </c>
       <c r="K185" s="4" t="inlineStr"/>
       <c r="L185" s="4" t="inlineStr"/>
-      <c r="M185" s="5" t="inlineStr"/>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N185" s="6" t="inlineStr"/>
       <c r="O185" s="5" t="inlineStr"/>
     </row>
@@ -15903,7 +16639,11 @@
       </c>
       <c r="K186" s="4" t="inlineStr"/>
       <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="5" t="inlineStr"/>
+      <c r="M186" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N186" s="6" t="inlineStr"/>
       <c r="O186" s="5" t="inlineStr"/>
     </row>
@@ -15952,7 +16692,11 @@
       </c>
       <c r="K187" s="4" t="inlineStr"/>
       <c r="L187" s="4" t="inlineStr"/>
-      <c r="M187" s="5" t="inlineStr"/>
+      <c r="M187" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N187" s="6" t="inlineStr"/>
       <c r="O187" s="5" t="inlineStr"/>
     </row>
@@ -16001,7 +16745,11 @@
       </c>
       <c r="K188" s="4" t="inlineStr"/>
       <c r="L188" s="4" t="inlineStr"/>
-      <c r="M188" s="5" t="inlineStr"/>
+      <c r="M188" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N188" s="6" t="inlineStr"/>
       <c r="O188" s="5" t="inlineStr"/>
     </row>
@@ -16056,7 +16804,11 @@
       <c r="L189" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M189" s="5" t="inlineStr"/>
+      <c r="M189" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N189" s="6" t="inlineStr"/>
       <c r="O189" s="5" t="inlineStr"/>
     </row>
@@ -16111,7 +16863,11 @@
       <c r="L190" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M190" s="5" t="inlineStr"/>
+      <c r="M190" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N190" s="6" t="inlineStr"/>
       <c r="O190" s="5" t="inlineStr"/>
     </row>
@@ -16160,7 +16916,11 @@
       </c>
       <c r="K191" s="4" t="inlineStr"/>
       <c r="L191" s="4" t="inlineStr"/>
-      <c r="M191" s="5" t="inlineStr"/>
+      <c r="M191" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N191" s="6" t="inlineStr"/>
       <c r="O191" s="5" t="inlineStr"/>
     </row>
@@ -16209,7 +16969,11 @@
       </c>
       <c r="K192" s="4" t="inlineStr"/>
       <c r="L192" s="4" t="inlineStr"/>
-      <c r="M192" s="5" t="inlineStr"/>
+      <c r="M192" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N192" s="6" t="inlineStr"/>
       <c r="O192" s="5" t="inlineStr"/>
     </row>
@@ -16258,7 +17022,11 @@
       </c>
       <c r="K193" s="4" t="inlineStr"/>
       <c r="L193" s="4" t="inlineStr"/>
-      <c r="M193" s="5" t="inlineStr"/>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N193" s="6" t="inlineStr"/>
       <c r="O193" s="5" t="inlineStr"/>
     </row>
@@ -16313,7 +17081,11 @@
       <c r="L194" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M194" s="5" t="inlineStr"/>
+      <c r="M194" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N194" s="6" t="inlineStr"/>
       <c r="O194" s="5" t="inlineStr"/>
     </row>
@@ -16368,7 +17140,11 @@
       <c r="L195" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M195" s="5" t="inlineStr"/>
+      <c r="M195" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N195" s="6" t="inlineStr"/>
       <c r="O195" s="5" t="inlineStr"/>
     </row>
@@ -16417,7 +17193,11 @@
       </c>
       <c r="K196" s="4" t="inlineStr"/>
       <c r="L196" s="4" t="inlineStr"/>
-      <c r="M196" s="5" t="inlineStr"/>
+      <c r="M196" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N196" s="6" t="inlineStr"/>
       <c r="O196" s="5" t="inlineStr"/>
     </row>
@@ -16466,7 +17246,11 @@
       </c>
       <c r="K197" s="4" t="inlineStr"/>
       <c r="L197" s="4" t="inlineStr"/>
-      <c r="M197" s="5" t="inlineStr"/>
+      <c r="M197" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N197" s="6" t="inlineStr"/>
       <c r="O197" s="5" t="inlineStr"/>
     </row>
@@ -16521,7 +17305,11 @@
       <c r="L198" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M198" s="5" t="inlineStr"/>
+      <c r="M198" s="5" t="inlineStr">
+        <is>
+          <t>dev_反应池/dev_扩容反应池</t>
+        </is>
+      </c>
       <c r="N198" s="6" t="inlineStr"/>
       <c r="O198" s="5" t="inlineStr"/>
     </row>
@@ -16570,7 +17358,11 @@
       </c>
       <c r="K199" s="4" t="inlineStr"/>
       <c r="L199" s="4" t="inlineStr"/>
-      <c r="M199" s="5" t="inlineStr"/>
+      <c r="M199" s="5" t="inlineStr">
+        <is>
+          <t>dev_天有洪炉</t>
+        </is>
+      </c>
       <c r="N199" s="6" t="inlineStr"/>
       <c r="O199" s="5" t="inlineStr"/>
     </row>
@@ -16619,7 +17411,11 @@
       </c>
       <c r="K200" s="4" t="inlineStr"/>
       <c r="L200" s="4" t="inlineStr"/>
-      <c r="M200" s="5" t="inlineStr"/>
+      <c r="M200" s="5" t="inlineStr">
+        <is>
+          <t>dev_天有洪炉</t>
+        </is>
+      </c>
       <c r="N200" s="6" t="inlineStr"/>
       <c r="O200" s="5" t="inlineStr"/>
     </row>
@@ -16668,7 +17464,11 @@
       </c>
       <c r="K201" s="4" t="inlineStr"/>
       <c r="L201" s="4" t="inlineStr"/>
-      <c r="M201" s="5" t="inlineStr"/>
+      <c r="M201" s="5" t="inlineStr">
+        <is>
+          <t>dev_天有洪炉</t>
+        </is>
+      </c>
       <c r="N201" s="6" t="inlineStr"/>
       <c r="O201" s="5" t="inlineStr"/>
     </row>
@@ -16717,7 +17517,11 @@
       </c>
       <c r="K202" s="4" t="inlineStr"/>
       <c r="L202" s="4" t="inlineStr"/>
-      <c r="M202" s="5" t="inlineStr"/>
+      <c r="M202" s="5" t="inlineStr">
+        <is>
+          <t>dev_天有洪炉</t>
+        </is>
+      </c>
       <c r="N202" s="6" t="inlineStr"/>
       <c r="O202" s="5" t="inlineStr"/>
     </row>
@@ -16766,7 +17570,11 @@
       <c r="L203" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M203" s="5" t="inlineStr"/>
+      <c r="M203" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_液体</t>
+        </is>
+      </c>
       <c r="N203" s="6" t="inlineStr"/>
       <c r="O203" s="5" t="inlineStr"/>
     </row>
@@ -16815,12 +17623,12 @@
       </c>
       <c r="K204" s="4" t="inlineStr"/>
       <c r="L204" s="4" t="inlineStr"/>
-      <c r="M204" s="5" t="inlineStr"/>
-      <c r="N204" s="7" t="inlineStr">
-        <is>
-          <t>⚠疑似环境变体(同名同机器且物品种类相同,仅数量不同,请核对数量差异对应什么环境条件)</t>
-        </is>
-      </c>
+      <c r="M204" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_气体</t>
+        </is>
+      </c>
+      <c r="N204" s="7" t="n"/>
       <c r="O204" s="5" t="inlineStr"/>
     </row>
     <row r="205">
@@ -16868,10 +17676,14 @@
       </c>
       <c r="K205" s="4" t="inlineStr"/>
       <c r="L205" s="4" t="inlineStr"/>
-      <c r="M205" s="5" t="inlineStr"/>
+      <c r="M205" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_气体</t>
+        </is>
+      </c>
       <c r="N205" s="7" t="inlineStr">
         <is>
-          <t>⚠疑似环境变体(同名同机器且物品种类相同,仅数量不同,请核对数量差异对应什么环境条件)</t>
+          <t>需求惰气环境（一台接通至少30min惰气的气体散布机会将以自身为中心13x13的地格变为惰气环境，此时若提纯机完全处于惰气环境范围内，即可启用此配方。若提纯机没有完全被惰气环境覆盖，则不视为满足惰气环境）</t>
         </is>
       </c>
       <c r="O205" s="5" t="inlineStr"/>
@@ -16921,12 +17733,12 @@
       </c>
       <c r="K206" s="4" t="inlineStr"/>
       <c r="L206" s="4" t="inlineStr"/>
-      <c r="M206" s="5" t="inlineStr"/>
-      <c r="N206" s="7" t="inlineStr">
-        <is>
-          <t>⚠疑似环境变体(同名同机器且物品种类相同,仅数量不同,请核对数量差异对应什么环境条件)</t>
-        </is>
-      </c>
+      <c r="M206" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_气体</t>
+        </is>
+      </c>
+      <c r="N206" s="7" t="n"/>
       <c r="O206" s="5" t="inlineStr"/>
     </row>
     <row r="207">
@@ -16974,10 +17786,14 @@
       </c>
       <c r="K207" s="4" t="inlineStr"/>
       <c r="L207" s="4" t="inlineStr"/>
-      <c r="M207" s="5" t="inlineStr"/>
+      <c r="M207" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_气体</t>
+        </is>
+      </c>
       <c r="N207" s="7" t="inlineStr">
         <is>
-          <t>⚠疑似环境变体(同名同机器且物品种类相同,仅数量不同,请核对数量差异对应什么环境条件)</t>
+          <t>需求惰气环境</t>
         </is>
       </c>
       <c r="O207" s="5" t="inlineStr"/>
@@ -17027,7 +17843,11 @@
       <c r="L208" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M208" s="5" t="inlineStr"/>
+      <c r="M208" s="5" t="inlineStr">
+        <is>
+          <t>dev_提纯机_液体</t>
+        </is>
+      </c>
       <c r="N208" s="6" t="inlineStr"/>
       <c r="O208" s="5" t="inlineStr"/>
     </row>
@@ -17076,7 +17896,11 @@
       <c r="L209" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M209" s="5" t="inlineStr"/>
+      <c r="M209" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N209" s="6" t="inlineStr"/>
       <c r="O209" s="5" t="inlineStr"/>
     </row>
@@ -17125,7 +17949,11 @@
       <c r="L210" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M210" s="5" t="inlineStr"/>
+      <c r="M210" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N210" s="6" t="inlineStr"/>
       <c r="O210" s="5" t="inlineStr"/>
     </row>
@@ -17174,7 +18002,11 @@
       <c r="L211" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M211" s="5" t="inlineStr"/>
+      <c r="M211" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N211" s="6" t="inlineStr"/>
       <c r="O211" s="5" t="inlineStr"/>
     </row>
@@ -17223,7 +18055,11 @@
       <c r="L212" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M212" s="5" t="inlineStr"/>
+      <c r="M212" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N212" s="6" t="inlineStr"/>
       <c r="O212" s="5" t="inlineStr"/>
     </row>
@@ -17272,7 +18108,11 @@
       <c r="L213" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M213" s="5" t="inlineStr"/>
+      <c r="M213" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N213" s="6" t="inlineStr"/>
       <c r="O213" s="5" t="inlineStr"/>
     </row>
@@ -17321,7 +18161,11 @@
       <c r="L214" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M214" s="5" t="inlineStr"/>
+      <c r="M214" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N214" s="6" t="inlineStr"/>
       <c r="O214" s="5" t="inlineStr"/>
     </row>
@@ -17370,7 +18214,11 @@
       <c r="L215" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M215" s="5" t="inlineStr"/>
+      <c r="M215" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N215" s="6" t="inlineStr"/>
       <c r="O215" s="5" t="inlineStr"/>
     </row>
@@ -17419,7 +18267,11 @@
       <c r="L216" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M216" s="5" t="inlineStr"/>
+      <c r="M216" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N216" s="6" t="inlineStr"/>
       <c r="O216" s="5" t="inlineStr"/>
     </row>
@@ -17468,7 +18320,11 @@
       <c r="L217" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M217" s="5" t="inlineStr"/>
+      <c r="M217" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N217" s="6" t="inlineStr"/>
       <c r="O217" s="5" t="inlineStr"/>
     </row>
@@ -17517,7 +18373,11 @@
       <c r="L218" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M218" s="5" t="inlineStr"/>
+      <c r="M218" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N218" s="6" t="inlineStr"/>
       <c r="O218" s="5" t="inlineStr"/>
     </row>
@@ -17566,7 +18426,11 @@
       <c r="L219" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M219" s="5" t="inlineStr"/>
+      <c r="M219" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N219" s="6" t="inlineStr"/>
       <c r="O219" s="5" t="inlineStr"/>
     </row>
@@ -17615,7 +18479,11 @@
       <c r="L220" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M220" s="5" t="inlineStr"/>
+      <c r="M220" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N220" s="6" t="inlineStr"/>
       <c r="O220" s="5" t="inlineStr"/>
     </row>
@@ -17664,7 +18532,11 @@
       <c r="L221" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M221" s="5" t="inlineStr"/>
+      <c r="M221" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N221" s="6" t="inlineStr"/>
       <c r="O221" s="5" t="inlineStr"/>
     </row>
@@ -17713,7 +18585,11 @@
       <c r="L222" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M222" s="5" t="inlineStr"/>
+      <c r="M222" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N222" s="6" t="inlineStr"/>
       <c r="O222" s="5" t="inlineStr"/>
     </row>
@@ -17762,7 +18638,11 @@
       <c r="L223" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M223" s="5" t="inlineStr"/>
+      <c r="M223" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N223" s="6" t="inlineStr"/>
       <c r="O223" s="5" t="inlineStr"/>
     </row>
@@ -17811,7 +18691,11 @@
       <c r="L224" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M224" s="5" t="inlineStr"/>
+      <c r="M224" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N224" s="6" t="inlineStr"/>
       <c r="O224" s="5" t="inlineStr"/>
     </row>
@@ -17860,7 +18744,11 @@
       <c r="L225" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M225" s="5" t="inlineStr"/>
+      <c r="M225" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N225" s="6" t="inlineStr"/>
       <c r="O225" s="5" t="inlineStr"/>
     </row>
@@ -17909,7 +18797,11 @@
       <c r="L226" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M226" s="5" t="inlineStr"/>
+      <c r="M226" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N226" s="6" t="inlineStr"/>
       <c r="O226" s="5" t="inlineStr"/>
     </row>
@@ -17958,7 +18850,11 @@
       <c r="L227" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M227" s="5" t="inlineStr"/>
+      <c r="M227" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N227" s="6" t="inlineStr"/>
       <c r="O227" s="5" t="inlineStr"/>
     </row>
@@ -18007,7 +18903,11 @@
       <c r="L228" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M228" s="5" t="inlineStr"/>
+      <c r="M228" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N228" s="6" t="inlineStr"/>
       <c r="O228" s="5" t="inlineStr"/>
     </row>
@@ -18056,7 +18956,11 @@
       <c r="L229" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M229" s="5" t="inlineStr"/>
+      <c r="M229" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N229" s="6" t="inlineStr"/>
       <c r="O229" s="5" t="inlineStr"/>
     </row>
@@ -18105,7 +19009,11 @@
       <c r="L230" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M230" s="5" t="inlineStr"/>
+      <c r="M230" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N230" s="6" t="inlineStr"/>
       <c r="O230" s="5" t="inlineStr"/>
     </row>
@@ -18154,7 +19062,11 @@
       <c r="L231" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M231" s="5" t="inlineStr"/>
+      <c r="M231" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N231" s="6" t="inlineStr"/>
       <c r="O231" s="5" t="inlineStr"/>
     </row>
@@ -18203,7 +19115,11 @@
       <c r="L232" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M232" s="5" t="inlineStr"/>
+      <c r="M232" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N232" s="6" t="inlineStr"/>
       <c r="O232" s="5" t="inlineStr"/>
     </row>
@@ -18252,7 +19168,11 @@
       <c r="L233" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M233" s="5" t="inlineStr"/>
+      <c r="M233" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N233" s="6" t="inlineStr"/>
       <c r="O233" s="5" t="inlineStr"/>
     </row>
@@ -18301,7 +19221,11 @@
       <c r="L234" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M234" s="5" t="inlineStr"/>
+      <c r="M234" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N234" s="6" t="inlineStr"/>
       <c r="O234" s="5" t="inlineStr"/>
     </row>
@@ -18350,7 +19274,11 @@
       <c r="L235" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M235" s="5" t="inlineStr"/>
+      <c r="M235" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N235" s="6" t="inlineStr"/>
       <c r="O235" s="5" t="inlineStr"/>
     </row>
@@ -18399,7 +19327,11 @@
       <c r="L236" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M236" s="5" t="inlineStr"/>
+      <c r="M236" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N236" s="6" t="inlineStr"/>
       <c r="O236" s="5" t="inlineStr"/>
     </row>
@@ -18448,7 +19380,11 @@
       <c r="L237" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M237" s="5" t="inlineStr"/>
+      <c r="M237" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N237" s="6" t="inlineStr"/>
       <c r="O237" s="5" t="inlineStr"/>
     </row>
@@ -18497,7 +19433,11 @@
       <c r="L238" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M238" s="5" t="inlineStr"/>
+      <c r="M238" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N238" s="6" t="inlineStr"/>
       <c r="O238" s="5" t="inlineStr"/>
     </row>
@@ -18546,7 +19486,11 @@
       <c r="L239" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M239" s="5" t="inlineStr"/>
+      <c r="M239" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N239" s="6" t="inlineStr"/>
       <c r="O239" s="5" t="inlineStr"/>
     </row>
@@ -18595,7 +19539,11 @@
       <c r="L240" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M240" s="5" t="inlineStr"/>
+      <c r="M240" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N240" s="6" t="inlineStr"/>
       <c r="O240" s="5" t="inlineStr"/>
     </row>
@@ -18644,7 +19592,11 @@
       <c r="L241" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M241" s="5" t="inlineStr"/>
+      <c r="M241" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N241" s="6" t="inlineStr"/>
       <c r="O241" s="5" t="inlineStr"/>
     </row>
@@ -18693,7 +19645,11 @@
       <c r="L242" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M242" s="5" t="inlineStr"/>
+      <c r="M242" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N242" s="6" t="inlineStr"/>
       <c r="O242" s="5" t="inlineStr"/>
     </row>
@@ -18742,7 +19698,11 @@
       <c r="L243" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M243" s="5" t="inlineStr"/>
+      <c r="M243" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N243" s="6" t="inlineStr"/>
       <c r="O243" s="5" t="inlineStr"/>
     </row>
@@ -18791,7 +19751,11 @@
       <c r="L244" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M244" s="5" t="inlineStr"/>
+      <c r="M244" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N244" s="6" t="inlineStr"/>
       <c r="O244" s="5" t="inlineStr"/>
     </row>
@@ -18840,7 +19804,11 @@
       <c r="L245" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M245" s="5" t="inlineStr"/>
+      <c r="M245" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N245" s="6" t="inlineStr"/>
       <c r="O245" s="5" t="inlineStr"/>
     </row>
@@ -18889,7 +19857,11 @@
       <c r="L246" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M246" s="5" t="inlineStr"/>
+      <c r="M246" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N246" s="6" t="inlineStr"/>
       <c r="O246" s="5" t="inlineStr"/>
     </row>
@@ -18938,7 +19910,11 @@
       <c r="L247" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M247" s="5" t="inlineStr"/>
+      <c r="M247" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N247" s="6" t="inlineStr"/>
       <c r="O247" s="5" t="inlineStr"/>
     </row>
@@ -18987,7 +19963,11 @@
       <c r="L248" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M248" s="5" t="inlineStr"/>
+      <c r="M248" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N248" s="6" t="inlineStr"/>
       <c r="O248" s="5" t="inlineStr"/>
     </row>
@@ -19036,7 +20016,11 @@
       <c r="L249" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M249" s="5" t="inlineStr"/>
+      <c r="M249" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N249" s="6" t="inlineStr"/>
       <c r="O249" s="5" t="inlineStr"/>
     </row>
@@ -19085,7 +20069,11 @@
       <c r="L250" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M250" s="5" t="inlineStr"/>
+      <c r="M250" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N250" s="6" t="inlineStr"/>
       <c r="O250" s="5" t="inlineStr"/>
     </row>
@@ -19134,7 +20122,11 @@
       <c r="L251" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M251" s="5" t="inlineStr"/>
+      <c r="M251" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N251" s="6" t="inlineStr"/>
       <c r="O251" s="5" t="inlineStr"/>
     </row>
@@ -19183,7 +20175,11 @@
       <c r="L252" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M252" s="5" t="inlineStr"/>
+      <c r="M252" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N252" s="6" t="inlineStr"/>
       <c r="O252" s="5" t="inlineStr"/>
     </row>
@@ -19232,7 +20228,11 @@
       <c r="L253" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M253" s="5" t="inlineStr"/>
+      <c r="M253" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N253" s="6" t="inlineStr"/>
       <c r="O253" s="5" t="inlineStr"/>
     </row>
@@ -19281,7 +20281,11 @@
       <c r="L254" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M254" s="5" t="inlineStr"/>
+      <c r="M254" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N254" s="6" t="inlineStr"/>
       <c r="O254" s="5" t="inlineStr"/>
     </row>
@@ -19330,7 +20334,11 @@
       <c r="L255" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M255" s="5" t="inlineStr"/>
+      <c r="M255" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N255" s="6" t="inlineStr"/>
       <c r="O255" s="5" t="inlineStr"/>
     </row>
@@ -19379,7 +20387,11 @@
       <c r="L256" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M256" s="5" t="inlineStr"/>
+      <c r="M256" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N256" s="6" t="inlineStr"/>
       <c r="O256" s="5" t="inlineStr"/>
     </row>
@@ -19428,7 +20440,11 @@
       <c r="L257" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M257" s="5" t="inlineStr"/>
+      <c r="M257" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N257" s="6" t="inlineStr"/>
       <c r="O257" s="5" t="inlineStr"/>
     </row>
@@ -19477,7 +20493,11 @@
       <c r="L258" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M258" s="5" t="inlineStr"/>
+      <c r="M258" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N258" s="6" t="inlineStr"/>
       <c r="O258" s="5" t="inlineStr"/>
     </row>
@@ -19526,7 +20546,11 @@
       <c r="L259" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M259" s="5" t="inlineStr"/>
+      <c r="M259" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N259" s="6" t="inlineStr"/>
       <c r="O259" s="5" t="inlineStr"/>
     </row>
@@ -19575,7 +20599,11 @@
       <c r="L260" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M260" s="5" t="inlineStr"/>
+      <c r="M260" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N260" s="6" t="inlineStr"/>
       <c r="O260" s="5" t="inlineStr"/>
     </row>
@@ -19624,7 +20652,11 @@
       <c r="L261" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M261" s="5" t="inlineStr"/>
+      <c r="M261" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N261" s="6" t="inlineStr"/>
       <c r="O261" s="5" t="inlineStr"/>
     </row>
@@ -19673,7 +20705,11 @@
       <c r="L262" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M262" s="5" t="inlineStr"/>
+      <c r="M262" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N262" s="6" t="inlineStr"/>
       <c r="O262" s="5" t="inlineStr"/>
     </row>
@@ -19722,7 +20758,11 @@
       <c r="L263" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M263" s="5" t="inlineStr"/>
+      <c r="M263" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N263" s="6" t="inlineStr"/>
       <c r="O263" s="5" t="inlineStr"/>
     </row>
@@ -19771,7 +20811,11 @@
       <c r="L264" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M264" s="5" t="inlineStr"/>
+      <c r="M264" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N264" s="6" t="inlineStr"/>
       <c r="O264" s="5" t="inlineStr"/>
     </row>
@@ -19820,7 +20864,11 @@
       <c r="L265" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M265" s="5" t="inlineStr"/>
+      <c r="M265" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N265" s="6" t="inlineStr"/>
       <c r="O265" s="5" t="inlineStr"/>
     </row>
@@ -19869,7 +20917,11 @@
       <c r="L266" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M266" s="5" t="inlineStr"/>
+      <c r="M266" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N266" s="6" t="inlineStr"/>
       <c r="O266" s="5" t="inlineStr"/>
     </row>
@@ -19918,7 +20970,11 @@
       <c r="L267" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M267" s="5" t="inlineStr"/>
+      <c r="M267" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N267" s="6" t="inlineStr"/>
       <c r="O267" s="5" t="inlineStr"/>
     </row>
@@ -19967,7 +21023,11 @@
       <c r="L268" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M268" s="5" t="inlineStr"/>
+      <c r="M268" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N268" s="6" t="inlineStr"/>
       <c r="O268" s="5" t="inlineStr"/>
     </row>
@@ -20016,7 +21076,11 @@
       <c r="L269" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M269" s="5" t="inlineStr"/>
+      <c r="M269" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N269" s="6" t="inlineStr"/>
       <c r="O269" s="5" t="inlineStr"/>
     </row>
@@ -20065,7 +21129,11 @@
       <c r="L270" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M270" s="5" t="inlineStr"/>
+      <c r="M270" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N270" s="6" t="inlineStr"/>
       <c r="O270" s="5" t="inlineStr"/>
     </row>
@@ -20114,7 +21182,11 @@
       <c r="L271" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M271" s="5" t="inlineStr"/>
+      <c r="M271" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N271" s="6" t="inlineStr"/>
       <c r="O271" s="5" t="inlineStr"/>
     </row>
@@ -20163,7 +21235,11 @@
       <c r="L272" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M272" s="5" t="inlineStr"/>
+      <c r="M272" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N272" s="6" t="inlineStr"/>
       <c r="O272" s="5" t="inlineStr"/>
     </row>
@@ -20212,7 +21288,11 @@
       <c r="L273" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M273" s="5" t="inlineStr"/>
+      <c r="M273" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N273" s="6" t="inlineStr"/>
       <c r="O273" s="5" t="inlineStr"/>
     </row>
@@ -20261,7 +21341,11 @@
       <c r="L274" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M274" s="5" t="inlineStr"/>
+      <c r="M274" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N274" s="6" t="inlineStr"/>
       <c r="O274" s="5" t="inlineStr"/>
     </row>
@@ -20310,7 +21394,11 @@
       <c r="L275" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M275" s="5" t="inlineStr"/>
+      <c r="M275" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N275" s="6" t="inlineStr"/>
       <c r="O275" s="5" t="inlineStr"/>
     </row>
@@ -20359,7 +21447,11 @@
       <c r="L276" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M276" s="5" t="inlineStr"/>
+      <c r="M276" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N276" s="6" t="inlineStr"/>
       <c r="O276" s="5" t="inlineStr"/>
     </row>
@@ -20408,7 +21500,11 @@
       <c r="L277" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M277" s="5" t="inlineStr"/>
+      <c r="M277" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N277" s="6" t="inlineStr"/>
       <c r="O277" s="5" t="inlineStr"/>
     </row>
@@ -20457,7 +21553,11 @@
       <c r="L278" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M278" s="5" t="inlineStr"/>
+      <c r="M278" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N278" s="6" t="inlineStr"/>
       <c r="O278" s="5" t="inlineStr"/>
     </row>
@@ -20506,7 +21606,11 @@
       <c r="L279" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M279" s="5" t="inlineStr"/>
+      <c r="M279" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N279" s="6" t="inlineStr"/>
       <c r="O279" s="5" t="inlineStr"/>
     </row>
@@ -20555,7 +21659,11 @@
       <c r="L280" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M280" s="5" t="inlineStr"/>
+      <c r="M280" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N280" s="6" t="inlineStr"/>
       <c r="O280" s="5" t="inlineStr"/>
     </row>
@@ -20604,7 +21712,11 @@
       <c r="L281" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M281" s="5" t="inlineStr"/>
+      <c r="M281" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N281" s="6" t="inlineStr"/>
       <c r="O281" s="5" t="inlineStr"/>
     </row>
@@ -20653,7 +21765,11 @@
       <c r="L282" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M282" s="5" t="inlineStr"/>
+      <c r="M282" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N282" s="6" t="inlineStr"/>
       <c r="O282" s="5" t="inlineStr"/>
     </row>
@@ -20702,7 +21818,11 @@
       <c r="L283" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M283" s="5" t="inlineStr"/>
+      <c r="M283" s="5" t="inlineStr">
+        <is>
+          <t>dev_拆解机</t>
+        </is>
+      </c>
       <c r="N283" s="6" t="inlineStr"/>
       <c r="O283" s="5" t="inlineStr"/>
     </row>
@@ -20745,8 +21865,16 @@
       </c>
       <c r="K284" s="4" t="inlineStr"/>
       <c r="L284" s="4" t="inlineStr"/>
-      <c r="M284" s="5" t="inlineStr"/>
-      <c r="N284" s="6" t="inlineStr"/>
+      <c r="M284" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N284" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤（即从设备上方的流体口单独接入一条至少6/min的液化息壤）</t>
+        </is>
+      </c>
       <c r="O284" s="5" t="inlineStr"/>
     </row>
     <row r="285">
@@ -20788,8 +21916,16 @@
       </c>
       <c r="K285" s="4" t="inlineStr"/>
       <c r="L285" s="4" t="inlineStr"/>
-      <c r="M285" s="5" t="inlineStr"/>
-      <c r="N285" s="6" t="inlineStr"/>
+      <c r="M285" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N285" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O285" s="5" t="inlineStr"/>
     </row>
     <row r="286">
@@ -20831,8 +21967,16 @@
       </c>
       <c r="K286" s="4" t="inlineStr"/>
       <c r="L286" s="4" t="inlineStr"/>
-      <c r="M286" s="5" t="inlineStr"/>
-      <c r="N286" s="6" t="inlineStr"/>
+      <c r="M286" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N286" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O286" s="5" t="inlineStr"/>
     </row>
     <row r="287">
@@ -20874,8 +22018,16 @@
       </c>
       <c r="K287" s="4" t="inlineStr"/>
       <c r="L287" s="4" t="inlineStr"/>
-      <c r="M287" s="5" t="inlineStr"/>
-      <c r="N287" s="6" t="inlineStr"/>
+      <c r="M287" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N287" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O287" s="5" t="inlineStr"/>
     </row>
     <row r="288">
@@ -20917,8 +22069,16 @@
       </c>
       <c r="K288" s="4" t="inlineStr"/>
       <c r="L288" s="4" t="inlineStr"/>
-      <c r="M288" s="5" t="inlineStr"/>
-      <c r="N288" s="6" t="inlineStr"/>
+      <c r="M288" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N288" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O288" s="5" t="inlineStr"/>
     </row>
     <row r="289">
@@ -20960,8 +22120,16 @@
       </c>
       <c r="K289" s="4" t="inlineStr"/>
       <c r="L289" s="4" t="inlineStr"/>
-      <c r="M289" s="5" t="inlineStr"/>
-      <c r="N289" s="6" t="inlineStr"/>
+      <c r="M289" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N289" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O289" s="5" t="inlineStr"/>
     </row>
     <row r="290">
@@ -21003,8 +22171,16 @@
       </c>
       <c r="K290" s="4" t="inlineStr"/>
       <c r="L290" s="4" t="inlineStr"/>
-      <c r="M290" s="5" t="inlineStr"/>
-      <c r="N290" s="6" t="inlineStr"/>
+      <c r="M290" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N290" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O290" s="5" t="inlineStr"/>
     </row>
     <row r="291">
@@ -21046,8 +22222,16 @@
       </c>
       <c r="K291" s="4" t="inlineStr"/>
       <c r="L291" s="4" t="inlineStr"/>
-      <c r="M291" s="5" t="inlineStr"/>
-      <c r="N291" s="6" t="inlineStr"/>
+      <c r="M291" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N291" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O291" s="5" t="inlineStr"/>
     </row>
     <row r="292">
@@ -21089,8 +22273,16 @@
       </c>
       <c r="K292" s="4" t="inlineStr"/>
       <c r="L292" s="4" t="inlineStr"/>
-      <c r="M292" s="5" t="inlineStr"/>
-      <c r="N292" s="6" t="inlineStr"/>
+      <c r="M292" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N292" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O292" s="5" t="inlineStr"/>
     </row>
     <row r="293">
@@ -21132,8 +22324,16 @@
       </c>
       <c r="K293" s="4" t="inlineStr"/>
       <c r="L293" s="4" t="inlineStr"/>
-      <c r="M293" s="5" t="inlineStr"/>
-      <c r="N293" s="6" t="inlineStr"/>
+      <c r="M293" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N293" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O293" s="5" t="inlineStr"/>
     </row>
     <row r="294">
@@ -21175,8 +22375,16 @@
       </c>
       <c r="K294" s="4" t="inlineStr"/>
       <c r="L294" s="4" t="inlineStr"/>
-      <c r="M294" s="5" t="inlineStr"/>
-      <c r="N294" s="6" t="inlineStr"/>
+      <c r="M294" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N294" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O294" s="5" t="inlineStr"/>
     </row>
     <row r="295">
@@ -21218,8 +22426,16 @@
       </c>
       <c r="K295" s="4" t="inlineStr"/>
       <c r="L295" s="4" t="inlineStr"/>
-      <c r="M295" s="5" t="inlineStr"/>
-      <c r="N295" s="6" t="inlineStr"/>
+      <c r="M295" s="5" t="inlineStr">
+        <is>
+          <t>dev_液气转化机_液体产出</t>
+        </is>
+      </c>
+      <c r="N295" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的液化息壤</t>
+        </is>
+      </c>
       <c r="O295" s="5" t="inlineStr"/>
     </row>
     <row r="296">
@@ -21261,8 +22477,16 @@
       </c>
       <c r="K296" s="4" t="inlineStr"/>
       <c r="L296" s="4" t="inlineStr"/>
-      <c r="M296" s="5" t="inlineStr"/>
-      <c r="N296" s="6" t="inlineStr"/>
+      <c r="M296" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_固体产出</t>
+        </is>
+      </c>
+      <c r="N296" s="6" t="inlineStr">
+        <is>
+          <t>需求额外的息壤气（即从设备上方的流体口单独接入一条至少6/min的息壤气）</t>
+        </is>
+      </c>
       <c r="O296" s="5" t="inlineStr"/>
     </row>
     <row r="297">
@@ -21304,8 +22528,16 @@
       </c>
       <c r="K297" s="4" t="inlineStr"/>
       <c r="L297" s="4" t="inlineStr"/>
-      <c r="M297" s="5" t="inlineStr"/>
-      <c r="N297" s="6" t="inlineStr"/>
+      <c r="M297" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N297" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O297" s="5" t="inlineStr"/>
     </row>
     <row r="298">
@@ -21347,8 +22579,16 @@
       </c>
       <c r="K298" s="4" t="inlineStr"/>
       <c r="L298" s="4" t="inlineStr"/>
-      <c r="M298" s="5" t="inlineStr"/>
-      <c r="N298" s="6" t="inlineStr"/>
+      <c r="M298" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_固体产出</t>
+        </is>
+      </c>
+      <c r="N298" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O298" s="5" t="inlineStr"/>
     </row>
     <row r="299">
@@ -21390,8 +22630,16 @@
       </c>
       <c r="K299" s="4" t="inlineStr"/>
       <c r="L299" s="4" t="inlineStr"/>
-      <c r="M299" s="5" t="inlineStr"/>
-      <c r="N299" s="6" t="inlineStr"/>
+      <c r="M299" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_固体产出</t>
+        </is>
+      </c>
+      <c r="N299" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O299" s="5" t="inlineStr"/>
     </row>
     <row r="300">
@@ -21433,8 +22681,16 @@
       </c>
       <c r="K300" s="4" t="inlineStr"/>
       <c r="L300" s="4" t="inlineStr"/>
-      <c r="M300" s="5" t="inlineStr"/>
-      <c r="N300" s="6" t="inlineStr"/>
+      <c r="M300" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N300" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O300" s="5" t="inlineStr"/>
     </row>
     <row r="301">
@@ -21476,8 +22732,16 @@
       </c>
       <c r="K301" s="4" t="inlineStr"/>
       <c r="L301" s="4" t="inlineStr"/>
-      <c r="M301" s="5" t="inlineStr"/>
-      <c r="N301" s="6" t="inlineStr"/>
+      <c r="M301" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N301" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O301" s="5" t="inlineStr"/>
     </row>
     <row r="302">
@@ -21519,8 +22783,16 @@
       </c>
       <c r="K302" s="4" t="inlineStr"/>
       <c r="L302" s="4" t="inlineStr"/>
-      <c r="M302" s="5" t="inlineStr"/>
-      <c r="N302" s="6" t="inlineStr"/>
+      <c r="M302" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_固体产出</t>
+        </is>
+      </c>
+      <c r="N302" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O302" s="5" t="inlineStr"/>
     </row>
     <row r="303">
@@ -21562,8 +22834,16 @@
       </c>
       <c r="K303" s="4" t="inlineStr"/>
       <c r="L303" s="4" t="inlineStr"/>
-      <c r="M303" s="5" t="inlineStr"/>
-      <c r="N303" s="6" t="inlineStr"/>
+      <c r="M303" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N303" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O303" s="5" t="inlineStr"/>
     </row>
     <row r="304">
@@ -21605,8 +22885,16 @@
       </c>
       <c r="K304" s="4" t="inlineStr"/>
       <c r="L304" s="4" t="inlineStr"/>
-      <c r="M304" s="5" t="inlineStr"/>
-      <c r="N304" s="6" t="inlineStr"/>
+      <c r="M304" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_气体产出</t>
+        </is>
+      </c>
+      <c r="N304" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O304" s="5" t="inlineStr"/>
     </row>
     <row r="305">
@@ -21648,8 +22936,16 @@
       </c>
       <c r="K305" s="4" t="inlineStr"/>
       <c r="L305" s="4" t="inlineStr"/>
-      <c r="M305" s="5" t="inlineStr"/>
-      <c r="N305" s="6" t="inlineStr"/>
+      <c r="M305" s="5" t="inlineStr">
+        <is>
+          <t>dev_固气转化机_固体产出</t>
+        </is>
+      </c>
+      <c r="N305" s="6" t="inlineStr">
+        <is>
+          <t>需求息壤气环境</t>
+        </is>
+      </c>
       <c r="O305" s="5" t="inlineStr"/>
     </row>
     <row r="306">
@@ -21697,8 +22993,16 @@
       </c>
       <c r="K306" s="4" t="inlineStr"/>
       <c r="L306" s="4" t="inlineStr"/>
-      <c r="M306" s="5" t="inlineStr"/>
-      <c r="N306" s="6" t="inlineStr"/>
+      <c r="M306" s="5" t="inlineStr">
+        <is>
+          <t>dev_气体反应炉</t>
+        </is>
+      </c>
+      <c r="N306" s="6" t="inlineStr">
+        <is>
+          <t>需求酸气环境（与惰气环境类似，只是气体散布机需接通酸气）</t>
+        </is>
+      </c>
       <c r="O306" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/reference/items_recipes_template.xlsx
+++ b/reference/items_recipes_template.xlsx
@@ -17683,7 +17683,7 @@
       </c>
       <c r="N205" s="7" t="inlineStr">
         <is>
-          <t>需求惰气环境（一台接通至少30min惰气的气体散布机会将以自身为中心13x13的地格变为惰气环境，此时若提纯机完全处于惰气环境范围内，即可启用此配方。若提纯机没有完全被惰气环境覆盖，则不视为满足惰气环境）</t>
+          <t>需求惰气环境（一台接入速率至少30单位/min惰气的气体散布机会将以自身为中心13x13的地格变为惰气环境，此时若提纯机完全处于惰气环境范围内，即可启用此配方。若提纯机没有完全被惰气环境覆盖，则不视为满足惰气环境）</t>
         </is>
       </c>
       <c r="O205" s="5" t="inlineStr"/>
